--- a/automation/reports/Excel/Automation_Test_Report.xlsx
+++ b/automation/reports/Excel/Automation_Test_Report.xlsx
@@ -38,7 +38,7 @@
     <t>Error</t>
   </si>
   <si>
-    <t>423bd4df-d78c-4f4d-9da2-5a40d73d614b</t>
+    <t>53091172-cd8c-43ed-b05e-55a2c98a89f9</t>
   </si>
   <si>
     <t>Login Screen</t>
@@ -47,7 +47,7 @@
     <t>Module: Login Screen</t>
   </si>
   <si>
-    <t>[TC-LOGI-001] should validate Login Screen criteria 1</t>
+    <t>[TC-LOGI-001] Verify successful login with valid credentials</t>
   </si>
   <si>
     <t>passed</t>
@@ -56,151 +56,151 @@
     <t/>
   </si>
   <si>
-    <t>7f29a1a5-900c-4e4a-955b-e43c8f7e0170</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-002] should validate Login Screen criteria 2</t>
-  </si>
-  <si>
-    <t>61e9aef8-bf2c-403f-ae19-d957b0d08ed2</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-003] should validate Login Screen criteria 3</t>
-  </si>
-  <si>
-    <t>d88acb1a-ee47-4cd0-9210-fe13fd61ac12</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-004] should validate Login Screen criteria 4</t>
-  </si>
-  <si>
-    <t>1f0ff0d3-9ee4-462a-9424-ca8397b51858</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-005] should validate Login Screen criteria 5</t>
-  </si>
-  <si>
-    <t>c00e599d-5227-4c80-b6cc-02694fa0a750</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-006] should validate Login Screen criteria 6</t>
-  </si>
-  <si>
-    <t>2112cc1a-f08b-4f3a-99b4-1ffb79f7cac0</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-007] should validate Login Screen criteria 7</t>
-  </si>
-  <si>
-    <t>3a86a63e-2aa1-47e4-a522-df67954640bf</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-008] should validate Login Screen criteria 8</t>
-  </si>
-  <si>
-    <t>614b4731-bfe9-483f-9122-014b12eea9d2</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-009] should validate Login Screen criteria 9</t>
-  </si>
-  <si>
-    <t>8c3a842d-5109-46a7-8918-1478d7258209</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-010] should validate Login Screen criteria 10</t>
-  </si>
-  <si>
-    <t>986895a9-535a-4f55-a2e7-1154160c601c</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-011] should validate Login Screen criteria 11</t>
-  </si>
-  <si>
-    <t>3086620a-d7ae-488f-a511-db1c6938de68</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-012] should validate Login Screen criteria 12</t>
-  </si>
-  <si>
-    <t>5b19d809-7460-489c-bfe0-c4ffb8e07ebd</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-013] should validate Login Screen criteria 13</t>
-  </si>
-  <si>
-    <t>67e7b901-2a5d-4abf-85cd-7ec58d17710f</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-014] should validate Login Screen criteria 14</t>
-  </si>
-  <si>
-    <t>7970e287-199e-4cab-8590-6a8663489575</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-015] should validate Login Screen criteria 15</t>
-  </si>
-  <si>
-    <t>e75b9bd2-9e14-49d3-a41d-7bd3bb6f8421</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-016] should validate Login Screen criteria 16</t>
-  </si>
-  <si>
-    <t>aea8b118-0bd0-4fd1-bfa3-34be1109bf71</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-017] should validate Login Screen criteria 17</t>
-  </si>
-  <si>
-    <t>4a070e4d-69e4-41ad-b57c-22c3ba14d2f3</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-018] should validate Login Screen criteria 18</t>
-  </si>
-  <si>
-    <t>a58af442-cd1a-4a09-a2e3-8b423f93f90a</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-019] should validate Login Screen criteria 19</t>
-  </si>
-  <si>
-    <t>065110f5-b97d-4f58-a0bd-e9dc07bf347d</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-020] should validate Login Screen criteria 20</t>
-  </si>
-  <si>
-    <t>6a08e109-5f9c-4ed3-aac6-3fa5cfe52b3a</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-021] should validate Login Screen criteria 21</t>
-  </si>
-  <si>
-    <t>dc3a4c13-38ed-4550-9dbd-4e57a9df90b0</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-022] should validate Login Screen criteria 22</t>
-  </si>
-  <si>
-    <t>1be2c780-533f-417d-9408-375c4871fe40</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-023] should validate Login Screen criteria 23</t>
-  </si>
-  <si>
-    <t>f01ea757-58c8-478d-99ef-0e68193b94e7</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-024] should validate Login Screen criteria 24</t>
-  </si>
-  <si>
-    <t>a447a492-3a93-4ddf-a574-4fba0c932353</t>
-  </si>
-  <si>
-    <t>[TC-LOGI-025] should validate Login Screen criteria 25</t>
-  </si>
-  <si>
-    <t>837c0ab3-28a8-46b8-9c14-7ea5ef505ec4</t>
+    <t>b342bf74-7bd5-431e-b055-6e1614388753</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-002] Verify error message with invalid email format</t>
+  </si>
+  <si>
+    <t>a729c4e4-1b01-49ba-a18b-82b9b4d4818f</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-003] Verify error message with incorrect password</t>
+  </si>
+  <si>
+    <t>f04f73bc-d6a0-4b04-a0dc-6326d4a22b5b</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-004] Verify password field masks input by default</t>
+  </si>
+  <si>
+    <t>bdddde60-f1dd-477b-ba98-1fbfaae8ba61</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-005] Verify toggle password visibility works</t>
+  </si>
+  <si>
+    <t>86a001f3-d387-4ac1-b960-aa68db8ba5b6</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-006] Verify Forgot Password link redirects correctly</t>
+  </si>
+  <si>
+    <t>fd032252-ab8e-4181-a34c-a7a9ca557d89</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-007] Verify Register Here link redirects to registration</t>
+  </si>
+  <si>
+    <t>75c68bf5-4c18-418f-a860-92b54eb9b112</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-008] Verify login button disabled when fields are empty</t>
+  </si>
+  <si>
+    <t>06005afb-fa07-4328-9281-613f56f7769b</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-009] Verify login with unregistered email</t>
+  </si>
+  <si>
+    <t>bab14ddb-c8d6-4dc8-bcda-7447600f2763</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-010] Verify loading spinner appears during login request</t>
+  </si>
+  <si>
+    <t>fd0dc7af-c4db-4637-bce4-fdac4de9d8a4</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-011] Verify successful login redirects to Dashboard</t>
+  </si>
+  <si>
+    <t>3696cbd0-e4b9-4ae4-945a-2be090584137</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-012] Verify session token is stored after login</t>
+  </si>
+  <si>
+    <t>5ebfb53f-46ac-4bdd-9818-e318c1e29ba8</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-013] Verify Remember Me checkbox functionality</t>
+  </si>
+  <si>
+    <t>2c031f71-bb3d-4be3-b507-a36c0b1b3ada</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-014] Verify session persistence across tabs</t>
+  </si>
+  <si>
+    <t>3ee64b4d-8fb1-464e-b631-708741cca983</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-015] Verify login via Google SSO</t>
+  </si>
+  <si>
+    <t>0c500952-b8c8-4790-b723-f19594e5fc5b</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-016] Verify login via Apple SSO</t>
+  </si>
+  <si>
+    <t>49a042d7-3241-40a4-8aac-a2840aa98591</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-017] Verify login via Facebook SSO</t>
+  </si>
+  <si>
+    <t>6d8b64a5-c7fd-41f1-b1d2-bf5e7436efe1</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-018] Verify account lockout after 5 failed attempts</t>
+  </si>
+  <si>
+    <t>4504cf10-6f07-428a-bfbc-6849e1002d6d</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-019] Verify Enter key submits the login form</t>
+  </si>
+  <si>
+    <t>ccaa5dd2-fbee-4d22-ab85-1a35ee0694da</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-020] Verify validation errors clear on input change</t>
+  </si>
+  <si>
+    <t>b203b065-6938-4faa-8517-d59eb6bb45a7</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-021] Verify UI responsiveness on mobile viewport</t>
+  </si>
+  <si>
+    <t>72fc73aa-32ae-4ef0-a1c7-f42caeeda1e6</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-022] Verify accessibility tab order on login form</t>
+  </si>
+  <si>
+    <t>f91982f4-0613-4d9d-a0cd-3deed8bc8321</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-023] Verify login API timeout handling</t>
+  </si>
+  <si>
+    <t>b2f5617d-43a5-41c3-a819-e205bc8c747c</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-024] Verify back button behavior after login</t>
+  </si>
+  <si>
+    <t>1d711dd5-94dc-49f6-b8b5-69c7ca50b9f9</t>
+  </si>
+  <si>
+    <t>[TC-LOGI-025] Verify input sanitization on login fields</t>
+  </si>
+  <si>
+    <t>d6ce7f08-e83d-4861-bb34-bddb06e06569</t>
   </si>
   <si>
     <t>Register Screen</t>
@@ -209,154 +209,154 @@
     <t>Module: Register Screen</t>
   </si>
   <si>
-    <t>[TC-REGI-001] should validate Register Screen criteria 1</t>
-  </si>
-  <si>
-    <t>ed90c80b-45ae-4f11-b961-9185a71f981c</t>
-  </si>
-  <si>
-    <t>[TC-REGI-002] should validate Register Screen criteria 2</t>
-  </si>
-  <si>
-    <t>721e43a3-f71e-4bc1-a468-76cc893faca5</t>
-  </si>
-  <si>
-    <t>[TC-REGI-003] should validate Register Screen criteria 3</t>
-  </si>
-  <si>
-    <t>a008b950-ef14-4681-afec-d5e8ed3b5b3f</t>
-  </si>
-  <si>
-    <t>[TC-REGI-004] should validate Register Screen criteria 4</t>
-  </si>
-  <si>
-    <t>f1f2c091-499d-4792-aaa0-c25f88207740</t>
-  </si>
-  <si>
-    <t>[TC-REGI-005] should validate Register Screen criteria 5</t>
-  </si>
-  <si>
-    <t>43c23905-fa31-4e8c-adea-54db6790b0a7</t>
-  </si>
-  <si>
-    <t>[TC-REGI-006] should validate Register Screen criteria 6</t>
-  </si>
-  <si>
-    <t>17dde568-55f4-49df-9cc2-d36e64d40966</t>
-  </si>
-  <si>
-    <t>[TC-REGI-007] should validate Register Screen criteria 7</t>
-  </si>
-  <si>
-    <t>f31be7f6-59df-454e-ba7a-60d79fed224f</t>
-  </si>
-  <si>
-    <t>[TC-REGI-008] should validate Register Screen criteria 8</t>
-  </si>
-  <si>
-    <t>3d9850dc-8d0a-4b39-8855-9c5e28d10d6f</t>
-  </si>
-  <si>
-    <t>[TC-REGI-009] should validate Register Screen criteria 9</t>
-  </si>
-  <si>
-    <t>ddd15db6-cdf6-4e91-aabe-d96112766aea</t>
-  </si>
-  <si>
-    <t>[TC-REGI-010] should validate Register Screen criteria 10</t>
-  </si>
-  <si>
-    <t>46c20b6d-3ee5-4196-bfee-e3aa449cde7e</t>
-  </si>
-  <si>
-    <t>[TC-REGI-011] should validate Register Screen criteria 11</t>
-  </si>
-  <si>
-    <t>5c0a224d-37c9-4d4e-9b6c-1108bbc13303</t>
-  </si>
-  <si>
-    <t>[TC-REGI-012] should validate Register Screen criteria 12</t>
-  </si>
-  <si>
-    <t>756d42af-f426-48ea-99b4-6e82934a67ed</t>
-  </si>
-  <si>
-    <t>[TC-REGI-013] should validate Register Screen criteria 13</t>
-  </si>
-  <si>
-    <t>fe552f12-c904-4b05-bfde-90dcc298bc55</t>
-  </si>
-  <si>
-    <t>[TC-REGI-014] should validate Register Screen criteria 14</t>
-  </si>
-  <si>
-    <t>f0e1b74c-7d78-4d92-a995-59d50d8565b7</t>
-  </si>
-  <si>
-    <t>[TC-REGI-015] should validate Register Screen criteria 15</t>
-  </si>
-  <si>
-    <t>0444de94-2cd6-4d04-8aa3-4e2ad1c38df4</t>
-  </si>
-  <si>
-    <t>[TC-REGI-016] should validate Register Screen criteria 16</t>
-  </si>
-  <si>
-    <t>6d087446-d16b-4991-a83c-5fa2e1daee3a</t>
-  </si>
-  <si>
-    <t>[TC-REGI-017] should validate Register Screen criteria 17</t>
-  </si>
-  <si>
-    <t>f89b37d7-8005-4427-ade8-d1202c8b4990</t>
-  </si>
-  <si>
-    <t>[TC-REGI-018] should validate Register Screen criteria 18</t>
-  </si>
-  <si>
-    <t>9fb73f8c-51b1-4f87-85d3-540342f0c800</t>
-  </si>
-  <si>
-    <t>[TC-REGI-019] should validate Register Screen criteria 19</t>
-  </si>
-  <si>
-    <t>d7984ee9-4d40-478e-ad8e-bf37f32d7ec9</t>
-  </si>
-  <si>
-    <t>[TC-REGI-020] should validate Register Screen criteria 20</t>
-  </si>
-  <si>
-    <t>5f25bfea-748d-4e34-9e88-158f9a5968ca</t>
-  </si>
-  <si>
-    <t>[TC-REGI-021] should validate Register Screen criteria 21</t>
-  </si>
-  <si>
-    <t>a1e5864a-2e26-4f13-8c45-57d360efc2bb</t>
-  </si>
-  <si>
-    <t>[TC-REGI-022] should validate Register Screen criteria 22</t>
-  </si>
-  <si>
-    <t>d43c7e8a-1a7b-4f7b-8e56-55884c05f747</t>
-  </si>
-  <si>
-    <t>[TC-REGI-023] should validate Register Screen criteria 23</t>
-  </si>
-  <si>
-    <t>7cb106ba-1988-46de-abad-630f74fbdb57</t>
-  </si>
-  <si>
-    <t>[TC-REGI-024] should validate Register Screen criteria 24</t>
-  </si>
-  <si>
-    <t>ac493231-114a-4186-bf40-cb143bfe65a5</t>
-  </si>
-  <si>
-    <t>[TC-REGI-025] should validate Register Screen criteria 25</t>
-  </si>
-  <si>
-    <t>5c7e1e86-3661-4083-a103-5dd4a0793fb8</t>
+    <t>[TC-REGI-001] Verify successful registration with valid data</t>
+  </si>
+  <si>
+    <t>68a23e1e-2dea-4307-9a3d-121bd5ff46a8</t>
+  </si>
+  <si>
+    <t>[TC-REGI-002] Verify error on existing email address</t>
+  </si>
+  <si>
+    <t>f5e4046d-7ace-4970-bf7c-f2d2bf87dd20</t>
+  </si>
+  <si>
+    <t>[TC-REGI-003] Verify password strength indicator</t>
+  </si>
+  <si>
+    <t>b2c531cb-4a6e-47f6-9043-684dda19fe58</t>
+  </si>
+  <si>
+    <t>[TC-REGI-004] Verify password mismatch error in confirmation field</t>
+  </si>
+  <si>
+    <t>0aa77484-8f43-4183-9dd9-e093cc080faf</t>
+  </si>
+  <si>
+    <t>[TC-REGI-005] Verify terms and conditions checkbox validation</t>
+  </si>
+  <si>
+    <t>7976b563-9b6b-4ba4-a586-e358d72d6645</t>
+  </si>
+  <si>
+    <t>[TC-REGI-006] Verify email format validation</t>
+  </si>
+  <si>
+    <t>f0662428-6fea-469d-852e-3a3ae25bd56a</t>
+  </si>
+  <si>
+    <t>[TC-REGI-007] Verify registration button disabled until fields filled</t>
+  </si>
+  <si>
+    <t>7b660301-464d-4f77-a8fc-8466810741ed</t>
+  </si>
+  <si>
+    <t>[TC-REGI-008] Verify OTP sent after registration submission</t>
+  </si>
+  <si>
+    <t>7f331c05-3b42-4362-a6c7-cb03f74a9842</t>
+  </si>
+  <si>
+    <t>[TC-REGI-009] Verify resend OTP functionality</t>
+  </si>
+  <si>
+    <t>1ab2e8db-18c5-4bd1-85e7-083fafa022c6</t>
+  </si>
+  <si>
+    <t>[TC-REGI-010] Verify successful OTP verification redirects to home</t>
+  </si>
+  <si>
+    <t>40978a4a-9405-4a10-a5e7-d32a3dc84c76</t>
+  </si>
+  <si>
+    <t>[TC-REGI-011] Verify invalid OTP error handling</t>
+  </si>
+  <si>
+    <t>1270cc85-af42-48a5-a036-092935856d56</t>
+  </si>
+  <si>
+    <t>[TC-REGI-012] Verify registration via Google SSO</t>
+  </si>
+  <si>
+    <t>d6b26036-299a-4246-9ad7-f27533406cd4</t>
+  </si>
+  <si>
+    <t>[TC-REGI-013] Verify registration via Apple SSO</t>
+  </si>
+  <si>
+    <t>27971c82-5993-4d41-9af9-97f60c63f82b</t>
+  </si>
+  <si>
+    <t>[TC-REGI-014] Verify phone number formatting and validation</t>
+  </si>
+  <si>
+    <t>dcc80a50-a7d0-4c77-8b0a-e5366a0ba405</t>
+  </si>
+  <si>
+    <t>[TC-REGI-015] Verify optional fields can be left blank</t>
+  </si>
+  <si>
+    <t>d87c0873-87e0-4219-b732-6216e2927570</t>
+  </si>
+  <si>
+    <t>[TC-REGI-016] Verify profile picture upload during registration</t>
+  </si>
+  <si>
+    <t>3df86dcc-b925-41e4-b336-99c5be250b02</t>
+  </si>
+  <si>
+    <t>[TC-REGI-017] Verify max file size for profile picture</t>
+  </si>
+  <si>
+    <t>ef8b8126-d619-46dd-86e9-adfb337a95ca</t>
+  </si>
+  <si>
+    <t>[TC-REGI-018] Verify supported formats for profile picture</t>
+  </si>
+  <si>
+    <t>a4b51d19-21c4-41c3-82ea-bed0d58fea9b</t>
+  </si>
+  <si>
+    <t>[TC-REGI-019] Verify UI responsiveness on tablet viewport</t>
+  </si>
+  <si>
+    <t>dfeba903-023f-4976-b2f8-caf7f7133309</t>
+  </si>
+  <si>
+    <t>[TC-REGI-020] Verify accessibility contrast ratios</t>
+  </si>
+  <si>
+    <t>ac2cab23-526a-41a0-805c-f482e40162f3</t>
+  </si>
+  <si>
+    <t>[TC-REGI-021] Verify keyboard navigation through form</t>
+  </si>
+  <si>
+    <t>910283cd-1096-4a47-bab1-c56bfef47b61</t>
+  </si>
+  <si>
+    <t>[TC-REGI-022] Verify error messages are screen-reader accessible</t>
+  </si>
+  <si>
+    <t>69eab4c4-01e1-4a58-80c0-d4f861a66216</t>
+  </si>
+  <si>
+    <t>[TC-REGI-023] Verify back button returns to login screen</t>
+  </si>
+  <si>
+    <t>a0bdf652-54ac-4a89-aac6-62b541bd45c2</t>
+  </si>
+  <si>
+    <t>[TC-REGI-024] Verify loading state during registration API call</t>
+  </si>
+  <si>
+    <t>55211e0c-dbe9-4b1f-8cbc-657efdb4b39f</t>
+  </si>
+  <si>
+    <t>[TC-REGI-025] Verify secure transmission of password (HTTPS)</t>
+  </si>
+  <si>
+    <t>a8ea48e8-0059-40c1-b498-95a992bdc26b</t>
   </si>
   <si>
     <t>Dashboard Screen</t>
@@ -365,124 +365,124 @@
     <t>Module: Dashboard Screen</t>
   </si>
   <si>
-    <t>[TC-DASH-001] should validate Dashboard Screen criteria 1</t>
-  </si>
-  <si>
-    <t>4fdb332d-511c-4739-b41a-bdcc602be00e</t>
-  </si>
-  <si>
-    <t>[TC-DASH-002] should validate Dashboard Screen criteria 2</t>
-  </si>
-  <si>
-    <t>0a2dc787-6279-4e4d-b8a5-c3a9e4e0f81b</t>
-  </si>
-  <si>
-    <t>[TC-DASH-003] should validate Dashboard Screen criteria 3</t>
-  </si>
-  <si>
-    <t>b4455147-e035-4c30-b6aa-b6e014d64b8b</t>
-  </si>
-  <si>
-    <t>[TC-DASH-004] should validate Dashboard Screen criteria 4</t>
-  </si>
-  <si>
-    <t>450e6155-f53b-4477-b37b-00ef240b69d4</t>
-  </si>
-  <si>
-    <t>[TC-DASH-005] should validate Dashboard Screen criteria 5</t>
-  </si>
-  <si>
-    <t>f37ebf40-7dec-4a6d-b0f5-7a2b896e9226</t>
-  </si>
-  <si>
-    <t>[TC-DASH-006] should validate Dashboard Screen criteria 6</t>
-  </si>
-  <si>
-    <t>01a122a3-f97e-46ed-b403-8224dd58e479</t>
-  </si>
-  <si>
-    <t>[TC-DASH-007] should validate Dashboard Screen criteria 7</t>
-  </si>
-  <si>
-    <t>ad3315fa-b7f2-4fa8-85d9-9ed5e25e0569</t>
-  </si>
-  <si>
-    <t>[TC-DASH-008] should validate Dashboard Screen criteria 8</t>
-  </si>
-  <si>
-    <t>f7737b01-6759-4fdc-8bad-e7a12a78eb14</t>
-  </si>
-  <si>
-    <t>[TC-DASH-009] should validate Dashboard Screen criteria 9</t>
-  </si>
-  <si>
-    <t>23fc90f0-1c0e-443b-aad3-7396eb5597d7</t>
-  </si>
-  <si>
-    <t>[TC-DASH-010] should validate Dashboard Screen criteria 10</t>
-  </si>
-  <si>
-    <t>b0f1af35-5472-4250-ba7f-f5927a08c6f4</t>
-  </si>
-  <si>
-    <t>[TC-DASH-011] should validate Dashboard Screen criteria 11</t>
-  </si>
-  <si>
-    <t>54f1224f-7b9b-49a8-8bb7-9fedb0a4eb93</t>
-  </si>
-  <si>
-    <t>[TC-DASH-012] should validate Dashboard Screen criteria 12</t>
-  </si>
-  <si>
-    <t>995e2219-c5b4-4878-ae31-aeaadbd070fb</t>
-  </si>
-  <si>
-    <t>[TC-DASH-013] should validate Dashboard Screen criteria 13</t>
-  </si>
-  <si>
-    <t>61695e08-1e57-4aa3-b69b-5a3eca6a410f</t>
-  </si>
-  <si>
-    <t>[TC-DASH-014] should validate Dashboard Screen criteria 14</t>
-  </si>
-  <si>
-    <t>13a8494f-a748-47f1-a4a0-6d5c8f12d385</t>
-  </si>
-  <si>
-    <t>[TC-DASH-015] should validate Dashboard Screen criteria 15</t>
-  </si>
-  <si>
-    <t>6a5244e2-145a-4b04-93b7-a3ca12379ddc</t>
-  </si>
-  <si>
-    <t>[TC-DASH-016] should validate Dashboard Screen criteria 16</t>
-  </si>
-  <si>
-    <t>5d1bcbc6-4c4f-4040-be6f-b60972f7b700</t>
-  </si>
-  <si>
-    <t>[TC-DASH-017] should validate Dashboard Screen criteria 17</t>
-  </si>
-  <si>
-    <t>50f6c5c5-1709-4304-a78c-af69361b5b98</t>
-  </si>
-  <si>
-    <t>[TC-DASH-018] should validate Dashboard Screen criteria 18</t>
-  </si>
-  <si>
-    <t>01cff84b-15d5-49d1-bc2f-70b061027671</t>
-  </si>
-  <si>
-    <t>[TC-DASH-019] should validate Dashboard Screen criteria 19</t>
-  </si>
-  <si>
-    <t>6ff1799a-5a26-4a00-b43e-01e1165de958</t>
-  </si>
-  <si>
-    <t>[TC-DASH-020] should validate Dashboard Screen criteria 20</t>
-  </si>
-  <si>
-    <t>9cb7e782-dfbe-49e4-94bb-61941045b5e7</t>
+    <t>[TC-DASH-001] Verify Dashboard loads correctly after authentication</t>
+  </si>
+  <si>
+    <t>4a10126a-be7c-4e0a-9629-60a37046466a</t>
+  </si>
+  <si>
+    <t>[TC-DASH-002] Verify user profile summary is displayed</t>
+  </si>
+  <si>
+    <t>76d42f14-c310-4135-b63e-2265aead6bea</t>
+  </si>
+  <si>
+    <t>[TC-DASH-003] Verify recent activity feed loads</t>
+  </si>
+  <si>
+    <t>4f166cc0-6bcc-405f-874a-1284ef071450</t>
+  </si>
+  <si>
+    <t>[TC-DASH-004] Verify quick action buttons are clickable</t>
+  </si>
+  <si>
+    <t>6e1b4eb1-addd-4de4-ae80-075e1d1f3fec</t>
+  </si>
+  <si>
+    <t>[TC-DASH-005] Verify unread notifications count is accurate</t>
+  </si>
+  <si>
+    <t>6ed608e1-8fbd-4524-b41d-a690477e9f10</t>
+  </si>
+  <si>
+    <t>[TC-DASH-006] Verify clicking notification opens details</t>
+  </si>
+  <si>
+    <t>a1af1d94-5ab1-4dc3-b131-9cf9681f9c78</t>
+  </si>
+  <si>
+    <t>[TC-DASH-007] Verify navigation drawer opens and closes</t>
+  </si>
+  <si>
+    <t>3ca602d9-2639-426f-b919-416b73492c16</t>
+  </si>
+  <si>
+    <t>[TC-DASH-008] Verify search functionality returns results</t>
+  </si>
+  <si>
+    <t>e3b0019e-069a-4956-848d-372911d57354</t>
+  </si>
+  <si>
+    <t>[TC-DASH-009] Verify empty state when no activity exists</t>
+  </si>
+  <si>
+    <t>5ad8bf22-8563-4bfb-bd84-386a4e4ecd41</t>
+  </si>
+  <si>
+    <t>[TC-DASH-010] Verify dashboard statistics match backend data</t>
+  </si>
+  <si>
+    <t>1eaeff5e-2727-4058-8cc7-e0666b0f84c9</t>
+  </si>
+  <si>
+    <t>[TC-DASH-011] Verify pull-to-refresh updates dashboard data</t>
+  </si>
+  <si>
+    <t>96ac49c7-ef60-445b-8e84-f1fffd54a454</t>
+  </si>
+  <si>
+    <t>[TC-DASH-012] Verify infinite scrolling on activity feed</t>
+  </si>
+  <si>
+    <t>58d42788-a699-4c93-a531-f781bbcbf40b</t>
+  </si>
+  <si>
+    <t>[TC-DASH-013] Verify lazy loading of images on dashboard</t>
+  </si>
+  <si>
+    <t>40dc7996-dac5-454c-9376-daf7092c4d8f</t>
+  </si>
+  <si>
+    <t>[TC-DASH-014] Verify dashboard handles offline mode gracefully</t>
+  </si>
+  <si>
+    <t>3b586b3b-b43b-46fb-8f89-7589e6731c60</t>
+  </si>
+  <si>
+    <t>[TC-DASH-015] Verify dashboard UI on large desktop screens</t>
+  </si>
+  <si>
+    <t>cfb0c10d-06cb-4814-b02f-65a9c0bf8e77</t>
+  </si>
+  <si>
+    <t>[TC-DASH-016] Verify theme toggle applies dark mode</t>
+  </si>
+  <si>
+    <t>3704c19f-058f-4598-aba0-e89b213adf99</t>
+  </si>
+  <si>
+    <t>[TC-DASH-017] Verify theme toggle applies light mode</t>
+  </si>
+  <si>
+    <t>a8e39332-49bf-49b1-92f9-e2fe0cbfd93a</t>
+  </si>
+  <si>
+    <t>[TC-DASH-018] Verify language selector updates dashboard text</t>
+  </si>
+  <si>
+    <t>e2cdbf9d-e7f9-473f-af2f-6fdd858a7ff2</t>
+  </si>
+  <si>
+    <t>[TC-DASH-019] Verify logout button on dashboard works</t>
+  </si>
+  <si>
+    <t>f18e778e-8329-43e8-8875-c9f101b6acbe</t>
+  </si>
+  <si>
+    <t>[TC-DASH-020] Verify back button exits app from dashboard</t>
+  </si>
+  <si>
+    <t>11b59f8a-5a21-490a-af93-945b02d9d469</t>
   </si>
   <si>
     <t>Profile Screen</t>
@@ -491,154 +491,154 @@
     <t>Module: Profile Screen</t>
   </si>
   <si>
-    <t>[TC-PROF-001] should validate Profile Screen criteria 1</t>
-  </si>
-  <si>
-    <t>01fb65ce-d783-4006-abdc-a101ac361663</t>
-  </si>
-  <si>
-    <t>[TC-PROF-002] should validate Profile Screen criteria 2</t>
-  </si>
-  <si>
-    <t>f0ec9b29-fe75-4d0d-af61-9fe55bfa2fad</t>
-  </si>
-  <si>
-    <t>[TC-PROF-003] should validate Profile Screen criteria 3</t>
-  </si>
-  <si>
-    <t>a76b0a35-aaf9-4eb1-909a-05310f4368c5</t>
-  </si>
-  <si>
-    <t>[TC-PROF-004] should validate Profile Screen criteria 4</t>
-  </si>
-  <si>
-    <t>796a3ec7-6370-46a0-9760-c474b6fa10ae</t>
-  </si>
-  <si>
-    <t>[TC-PROF-005] should validate Profile Screen criteria 5</t>
-  </si>
-  <si>
-    <t>86f12336-8f93-44df-a168-4a9720dd5b21</t>
-  </si>
-  <si>
-    <t>[TC-PROF-006] should validate Profile Screen criteria 6</t>
-  </si>
-  <si>
-    <t>10f529cd-11a8-43a2-9afc-e77bf5d6fc34</t>
-  </si>
-  <si>
-    <t>[TC-PROF-007] should validate Profile Screen criteria 7</t>
-  </si>
-  <si>
-    <t>4bfb3dd0-1419-45cb-b8be-a0b24a2a39e9</t>
-  </si>
-  <si>
-    <t>[TC-PROF-008] should validate Profile Screen criteria 8</t>
-  </si>
-  <si>
-    <t>5eb7e5ed-2bd9-4100-9cca-7fa702ddf541</t>
-  </si>
-  <si>
-    <t>[TC-PROF-009] should validate Profile Screen criteria 9</t>
-  </si>
-  <si>
-    <t>bc2a9ccb-fdd2-4415-89a8-93ce8d302080</t>
-  </si>
-  <si>
-    <t>[TC-PROF-010] should validate Profile Screen criteria 10</t>
-  </si>
-  <si>
-    <t>4ea1496e-2d82-43a8-88d3-4866b9e28e7e</t>
-  </si>
-  <si>
-    <t>[TC-PROF-011] should validate Profile Screen criteria 11</t>
-  </si>
-  <si>
-    <t>4fa2f6d6-73ab-4564-a969-75ad62c3bc08</t>
-  </si>
-  <si>
-    <t>[TC-PROF-012] should validate Profile Screen criteria 12</t>
-  </si>
-  <si>
-    <t>82ca7c5e-9141-488d-ada8-bd4a6a3a8723</t>
-  </si>
-  <si>
-    <t>[TC-PROF-013] should validate Profile Screen criteria 13</t>
-  </si>
-  <si>
-    <t>c40e6a9d-a3e8-43a4-9692-a3d09af02ee1</t>
-  </si>
-  <si>
-    <t>[TC-PROF-014] should validate Profile Screen criteria 14</t>
-  </si>
-  <si>
-    <t>cb5889da-33a6-48f1-81e3-7b3fd12c9660</t>
-  </si>
-  <si>
-    <t>[TC-PROF-015] should validate Profile Screen criteria 15</t>
-  </si>
-  <si>
-    <t>21508256-6caf-4163-9a7d-0a8524c42729</t>
-  </si>
-  <si>
-    <t>[TC-PROF-016] should validate Profile Screen criteria 16</t>
-  </si>
-  <si>
-    <t>cdade55e-c050-4c1e-8864-0664d83e3883</t>
-  </si>
-  <si>
-    <t>[TC-PROF-017] should validate Profile Screen criteria 17</t>
-  </si>
-  <si>
-    <t>bf9dba9c-5891-45f6-a48b-1c9f5f9ad649</t>
-  </si>
-  <si>
-    <t>[TC-PROF-018] should validate Profile Screen criteria 18</t>
-  </si>
-  <si>
-    <t>f0809638-bf24-4308-861e-20311e4b043f</t>
-  </si>
-  <si>
-    <t>[TC-PROF-019] should validate Profile Screen criteria 19</t>
-  </si>
-  <si>
-    <t>22a9dccc-93a3-4bcc-bcfd-d081aa2a530c</t>
-  </si>
-  <si>
-    <t>[TC-PROF-020] should validate Profile Screen criteria 20</t>
-  </si>
-  <si>
-    <t>f7dfabe3-03fd-43c6-bc4e-a45a3321e084</t>
-  </si>
-  <si>
-    <t>[TC-PROF-021] should validate Profile Screen criteria 21</t>
-  </si>
-  <si>
-    <t>1dd25056-a301-4701-9849-c90f8f146a8d</t>
-  </si>
-  <si>
-    <t>[TC-PROF-022] should validate Profile Screen criteria 22</t>
-  </si>
-  <si>
-    <t>18f4b393-efe5-4e8a-9168-1121de7538d3</t>
-  </si>
-  <si>
-    <t>[TC-PROF-023] should validate Profile Screen criteria 23</t>
-  </si>
-  <si>
-    <t>2b4586c5-bb72-413e-8703-97b379fc84d3</t>
-  </si>
-  <si>
-    <t>[TC-PROF-024] should validate Profile Screen criteria 24</t>
-  </si>
-  <si>
-    <t>dbe08901-aad5-402d-9043-bffcd32889ae</t>
-  </si>
-  <si>
-    <t>[TC-PROF-025] should validate Profile Screen criteria 25</t>
-  </si>
-  <si>
-    <t>aecb5fe3-9c12-4057-ac14-e4921ff6c931</t>
+    <t>[TC-PROF-001] Verify user details are loaded correctly</t>
+  </si>
+  <si>
+    <t>45dce199-1617-4104-8612-ac978daab34c</t>
+  </si>
+  <si>
+    <t>[TC-PROF-002] Verify Edit Profile button enables form fields</t>
+  </si>
+  <si>
+    <t>e63060ea-0897-46a1-b9fe-c7682a6ee848</t>
+  </si>
+  <si>
+    <t>[TC-PROF-003] Verify saving profile updates backend data</t>
+  </si>
+  <si>
+    <t>3ecb771c-634e-4dc6-8f7f-0751c4a1c309</t>
+  </si>
+  <si>
+    <t>[TC-PROF-004] Verify canceling edit restores original data</t>
+  </si>
+  <si>
+    <t>e46e2575-0659-45b9-8c9a-97007481ad72</t>
+  </si>
+  <si>
+    <t>[TC-PROF-005] Verify name field validation (no special chars)</t>
+  </si>
+  <si>
+    <t>9ae20c03-90b9-492f-9600-88d2c54aaced</t>
+  </si>
+  <si>
+    <t>[TC-PROF-006] Verify bio character limit enforcement</t>
+  </si>
+  <si>
+    <t>323ff630-9050-4899-8eec-376699ce8258</t>
+  </si>
+  <si>
+    <t>[TC-PROF-007] Verify profile picture can be changed</t>
+  </si>
+  <si>
+    <t>cd4e3d28-f9a4-4689-ada5-061d9cd1fd20</t>
+  </si>
+  <si>
+    <t>[TC-PROF-008] Verify camera opens for new profile picture</t>
+  </si>
+  <si>
+    <t>bc394e2c-b4c6-410c-b832-4c41b562c107</t>
+  </si>
+  <si>
+    <t>[TC-PROF-009] Verify gallery opens for profile picture selection</t>
+  </si>
+  <si>
+    <t>38251119-9b60-416a-9317-bad7297340f5</t>
+  </si>
+  <si>
+    <t>[TC-PROF-010] Verify cropping functionality for profile picture</t>
+  </si>
+  <si>
+    <t>1f890289-f7e3-44f7-8914-68d63a8e44ee</t>
+  </si>
+  <si>
+    <t>[TC-PROF-011] Verify email update requires re-authentication</t>
+  </si>
+  <si>
+    <t>9b316d79-e11e-4607-a711-39db1b17e440</t>
+  </si>
+  <si>
+    <t>[TC-PROF-012] Verify password change from profile screen</t>
+  </si>
+  <si>
+    <t>2fa14afd-576b-4fa1-bbe1-de210f682222</t>
+  </si>
+  <si>
+    <t>[TC-PROF-013] Verify password change requires current password</t>
+  </si>
+  <si>
+    <t>7d3a7416-4edc-4967-8511-b39bc65a30f0</t>
+  </si>
+  <si>
+    <t>[TC-PROF-014] Verify delete account button opens confirmation</t>
+  </si>
+  <si>
+    <t>be77901f-902b-4de7-914f-efc358eeae29</t>
+  </si>
+  <si>
+    <t>[TC-PROF-015] Verify account deletion permanently removes user</t>
+  </si>
+  <si>
+    <t>2640dd92-77b0-425e-89f3-8e5d8f31d767</t>
+  </si>
+  <si>
+    <t>[TC-PROF-016] Verify privacy settings toggle switches</t>
+  </si>
+  <si>
+    <t>47014971-4833-4b83-9cb2-b1f48b634cec</t>
+  </si>
+  <si>
+    <t>[TC-PROF-017] Verify notification preferences save correctly</t>
+  </si>
+  <si>
+    <t>ba9db050-f7c8-457a-809a-b81f5b4fad34</t>
+  </si>
+  <si>
+    <t>[TC-PROF-018] Verify two-factor authentication toggle</t>
+  </si>
+  <si>
+    <t>a8b0f91b-533d-4c0d-beba-9c04106b2213</t>
+  </si>
+  <si>
+    <t>[TC-PROF-019] Verify 2FA setup process completes</t>
+  </si>
+  <si>
+    <t>958eb91a-2253-4426-be24-ca2cef832c7e</t>
+  </si>
+  <si>
+    <t>[TC-PROF-020] Verify linked accounts section displays integrations</t>
+  </si>
+  <si>
+    <t>8fa7aa65-cf2b-4f5b-aca2-b99d57dfbd6e</t>
+  </si>
+  <si>
+    <t>[TC-PROF-021] Verify unlinking a Google account works</t>
+  </si>
+  <si>
+    <t>982f121c-9d7a-432b-bef8-1db881aea82b</t>
+  </si>
+  <si>
+    <t>[TC-PROF-022] Verify download personal data feature</t>
+  </si>
+  <si>
+    <t>71c023de-b303-49cc-ae3a-bf8ab00e09e6</t>
+  </si>
+  <si>
+    <t>[TC-PROF-023] Verify UI breaks on extremely long names</t>
+  </si>
+  <si>
+    <t>52d0a4e4-14a3-4e12-92e1-6758dabf5e7c</t>
+  </si>
+  <si>
+    <t>[TC-PROF-024] Verify timezone setting updates properly</t>
+  </si>
+  <si>
+    <t>fe479c91-349c-450b-af06-b0f8e73e58f5</t>
+  </si>
+  <si>
+    <t>[TC-PROF-025] Verify profile screen load time under 2 seconds</t>
+  </si>
+  <si>
+    <t>bcd5c815-c140-4f91-a632-1972a23f653f</t>
   </si>
   <si>
     <t>Settings Screen</t>
@@ -647,154 +647,154 @@
     <t>Module: Settings Screen</t>
   </si>
   <si>
-    <t>[TC-SETT-001] should validate Settings Screen criteria 1</t>
-  </si>
-  <si>
-    <t>5ac2251a-23a9-4945-a55a-5cf5ee301f4d</t>
-  </si>
-  <si>
-    <t>[TC-SETT-002] should validate Settings Screen criteria 2</t>
-  </si>
-  <si>
-    <t>0cfa335c-3364-4850-b27a-02153ebff41d</t>
-  </si>
-  <si>
-    <t>[TC-SETT-003] should validate Settings Screen criteria 3</t>
-  </si>
-  <si>
-    <t>7f35780b-f308-4ac7-84e7-75264b0b54c2</t>
-  </si>
-  <si>
-    <t>[TC-SETT-004] should validate Settings Screen criteria 4</t>
-  </si>
-  <si>
-    <t>0593f0f5-a15e-4e94-9414-e5337dbd38c0</t>
-  </si>
-  <si>
-    <t>[TC-SETT-005] should validate Settings Screen criteria 5</t>
-  </si>
-  <si>
-    <t>de6d9fda-01e7-4aa9-a84a-26a4a15a673e</t>
-  </si>
-  <si>
-    <t>[TC-SETT-006] should validate Settings Screen criteria 6</t>
-  </si>
-  <si>
-    <t>7c28f8c3-8b3e-4706-a79e-16d97c320a2c</t>
-  </si>
-  <si>
-    <t>[TC-SETT-007] should validate Settings Screen criteria 7</t>
-  </si>
-  <si>
-    <t>113f42ee-2f62-4d88-9cf9-def8a1aa86b9</t>
-  </si>
-  <si>
-    <t>[TC-SETT-008] should validate Settings Screen criteria 8</t>
-  </si>
-  <si>
-    <t>35519b55-2cb4-47ef-bcb4-49476e706fcf</t>
-  </si>
-  <si>
-    <t>[TC-SETT-009] should validate Settings Screen criteria 9</t>
-  </si>
-  <si>
-    <t>0ba205d1-c212-4134-b5df-647dbb67ca40</t>
-  </si>
-  <si>
-    <t>[TC-SETT-010] should validate Settings Screen criteria 10</t>
-  </si>
-  <si>
-    <t>4933588d-8817-4f35-a590-7908399b43a3</t>
-  </si>
-  <si>
-    <t>[TC-SETT-011] should validate Settings Screen criteria 11</t>
-  </si>
-  <si>
-    <t>311fa2f3-a583-4fa7-9338-ae9d67fca7c6</t>
-  </si>
-  <si>
-    <t>[TC-SETT-012] should validate Settings Screen criteria 12</t>
-  </si>
-  <si>
-    <t>9357f970-e7f8-4daf-ba45-29dd945784b0</t>
-  </si>
-  <si>
-    <t>[TC-SETT-013] should validate Settings Screen criteria 13</t>
-  </si>
-  <si>
-    <t>f56e8d05-77c5-4754-b83e-950ad00ad95a</t>
-  </si>
-  <si>
-    <t>[TC-SETT-014] should validate Settings Screen criteria 14</t>
-  </si>
-  <si>
-    <t>5b5bc23e-0070-4e06-b2f4-024ff98e9508</t>
-  </si>
-  <si>
-    <t>[TC-SETT-015] should validate Settings Screen criteria 15</t>
-  </si>
-  <si>
-    <t>d6506177-2176-4000-91cd-93bf87ad2ece</t>
-  </si>
-  <si>
-    <t>[TC-SETT-016] should validate Settings Screen criteria 16</t>
-  </si>
-  <si>
-    <t>ac52cc2d-da6f-46f8-9998-daf637c24826</t>
-  </si>
-  <si>
-    <t>[TC-SETT-017] should validate Settings Screen criteria 17</t>
-  </si>
-  <si>
-    <t>8e9a7c9f-3415-4dbd-ae8c-f08fbca03068</t>
-  </si>
-  <si>
-    <t>[TC-SETT-018] should validate Settings Screen criteria 18</t>
-  </si>
-  <si>
-    <t>eb9261b3-70fa-4aa1-9519-7acaafd0e878</t>
-  </si>
-  <si>
-    <t>[TC-SETT-019] should validate Settings Screen criteria 19</t>
-  </si>
-  <si>
-    <t>306820f4-6c21-4328-bd50-0befa4b29b6d</t>
-  </si>
-  <si>
-    <t>[TC-SETT-020] should validate Settings Screen criteria 20</t>
-  </si>
-  <si>
-    <t>535d72fb-34cf-45fd-8b3c-0f78d4fe4e0a</t>
-  </si>
-  <si>
-    <t>[TC-SETT-021] should validate Settings Screen criteria 21</t>
-  </si>
-  <si>
-    <t>17145bfc-0750-4c7d-8ba3-3c9ffc0ed307</t>
-  </si>
-  <si>
-    <t>[TC-SETT-022] should validate Settings Screen criteria 22</t>
-  </si>
-  <si>
-    <t>534ee605-e314-45dd-b8ed-7556db632d79</t>
-  </si>
-  <si>
-    <t>[TC-SETT-023] should validate Settings Screen criteria 23</t>
-  </si>
-  <si>
-    <t>8ce76d7b-eb4f-42c8-954d-52f56d967289</t>
-  </si>
-  <si>
-    <t>[TC-SETT-024] should validate Settings Screen criteria 24</t>
-  </si>
-  <si>
-    <t>6926755a-2314-4f61-ba8c-3246542dc3c9</t>
-  </si>
-  <si>
-    <t>[TC-SETT-025] should validate Settings Screen criteria 25</t>
-  </si>
-  <si>
-    <t>070758c7-7703-495a-825b-2917774c2795</t>
+    <t>[TC-SETT-001] Verify settings screen loads sections correctly</t>
+  </si>
+  <si>
+    <t>64dd69c4-2463-42a6-b9db-46285ffd9a98</t>
+  </si>
+  <si>
+    <t>[TC-SETT-002] Verify app version is displayed at bottom</t>
+  </si>
+  <si>
+    <t>4b88e2d7-d963-4bc6-8434-d2387abd2d87</t>
+  </si>
+  <si>
+    <t>[TC-SETT-003] Verify clear cache button frees storage</t>
+  </si>
+  <si>
+    <t>cc759361-1a16-4e16-b2e1-fb25b7ffe218</t>
+  </si>
+  <si>
+    <t>[TC-SETT-004] Verify push notifications global toggle</t>
+  </si>
+  <si>
+    <t>0433b17d-93b6-4eb5-a55a-d44e054f8c78</t>
+  </si>
+  <si>
+    <t>[TC-SETT-005] Verify email notifications global toggle</t>
+  </si>
+  <si>
+    <t>fb147fd8-a5fd-4862-80c1-da316c8ec724</t>
+  </si>
+  <si>
+    <t>[TC-SETT-006] Verify SMS notifications global toggle</t>
+  </si>
+  <si>
+    <t>b32eb090-ccc1-4ca9-bb0d-02039f34d20c</t>
+  </si>
+  <si>
+    <t>[TC-SETT-007] Verify data usage settings (Wi-Fi only mode)</t>
+  </si>
+  <si>
+    <t>9f27caec-a576-4901-b594-6fb4bb4d1f27</t>
+  </si>
+  <si>
+    <t>[TC-SETT-008] Verify auto-play video settings</t>
+  </si>
+  <si>
+    <t>b776fdc2-6c82-4d02-acd2-1e83a6167f24</t>
+  </si>
+  <si>
+    <t>[TC-SETT-009] Verify location permissions toggle</t>
+  </si>
+  <si>
+    <t>1c32125a-0c83-45f3-8e2e-7850433d64ea</t>
+  </si>
+  <si>
+    <t>[TC-SETT-010] Verify camera permissions toggle</t>
+  </si>
+  <si>
+    <t>62e4b342-3742-4b5c-bd9a-8c0df33a9f9f</t>
+  </si>
+  <si>
+    <t>[TC-SETT-011] Verify microphone permissions toggle</t>
+  </si>
+  <si>
+    <t>5664f1d7-c201-4163-9d97-714cc1edbfb8</t>
+  </si>
+  <si>
+    <t>[TC-SETT-012] Verify contact sync functionality</t>
+  </si>
+  <si>
+    <t>288b8547-fbcf-4daa-8aa1-92145b0ee8ee</t>
+  </si>
+  <si>
+    <t>[TC-SETT-013] Verify default language selection</t>
+  </si>
+  <si>
+    <t>ef79adec-7f76-405b-b9cc-2b13111f9ebd</t>
+  </si>
+  <si>
+    <t>[TC-SETT-014] Verify default currency selection</t>
+  </si>
+  <si>
+    <t>781c4162-fadd-44c4-ba4a-89c18b49f5b4</t>
+  </si>
+  <si>
+    <t>[TC-SETT-015] Verify measurement unit toggle (Metric/Imperial)</t>
+  </si>
+  <si>
+    <t>2f39bd2a-0a47-41e8-8895-f97e8ef36637</t>
+  </si>
+  <si>
+    <t>[TC-SETT-016] Verify help and support link opens webview</t>
+  </si>
+  <si>
+    <t>8ece6abf-8053-4034-9ec6-e74bf21c79ed</t>
+  </si>
+  <si>
+    <t>[TC-SETT-017] Verify terms of service link opens webview</t>
+  </si>
+  <si>
+    <t>60022447-9b07-497d-81aa-b5f8fb884632</t>
+  </si>
+  <si>
+    <t>[TC-SETT-018] Verify privacy policy link opens webview</t>
+  </si>
+  <si>
+    <t>42774189-db53-4cc8-9b7c-4cd6c9f8249e</t>
+  </si>
+  <si>
+    <t>[TC-SETT-019] Verify open source licenses view</t>
+  </si>
+  <si>
+    <t>4a90eb5d-3a32-412f-a2a5-c621fbc2b001</t>
+  </si>
+  <si>
+    <t>[TC-SETT-020] Verify report a bug form submission</t>
+  </si>
+  <si>
+    <t>6de6cb9c-47da-4aa4-81be-f4d37e8bb835</t>
+  </si>
+  <si>
+    <t>[TC-SETT-021] Verify rate app redirects to app store</t>
+  </si>
+  <si>
+    <t>b845d29f-d633-4d9b-9206-5c8ef2bcc6fe</t>
+  </si>
+  <si>
+    <t>[TC-SETT-022] Verify developer mode hidden menu</t>
+  </si>
+  <si>
+    <t>df1da8e4-ff60-4119-b79e-36329b21658c</t>
+  </si>
+  <si>
+    <t>[TC-SETT-023] Verify beta features opt-in toggle</t>
+  </si>
+  <si>
+    <t>5592e35e-f4c5-43d2-af79-835a52a9c828</t>
+  </si>
+  <si>
+    <t>[TC-SETT-024] Verify account limits and quotas view</t>
+  </si>
+  <si>
+    <t>c1d7bb8f-efba-4208-893f-ccd3581a08c2</t>
+  </si>
+  <si>
+    <t>[TC-SETT-025] Verify sign out from all devices functionality</t>
+  </si>
+  <si>
+    <t>f5511cc7-81fc-4a1e-b648-81e906cddcfe</t>
   </si>
   <si>
     <t>Analyze Screen</t>
@@ -803,154 +803,154 @@
     <t>Module: Analyze Screen</t>
   </si>
   <si>
-    <t>[TC-ANAL-001] should validate Analyze Screen criteria 1</t>
-  </si>
-  <si>
-    <t>11e1b503-2b13-4859-b530-d305f1c16474</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-002] should validate Analyze Screen criteria 2</t>
-  </si>
-  <si>
-    <t>79d87d28-de36-4f2e-b353-762e17b21d9f</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-003] should validate Analyze Screen criteria 3</t>
-  </si>
-  <si>
-    <t>a484077f-beb3-47fb-9a6d-d52698eb54c9</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-004] should validate Analyze Screen criteria 4</t>
-  </si>
-  <si>
-    <t>7bb7c999-166e-4818-89c0-71399a0bb1ab</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-005] should validate Analyze Screen criteria 5</t>
-  </si>
-  <si>
-    <t>b0223d39-dd6b-4b4f-898b-b834953618d4</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-006] should validate Analyze Screen criteria 6</t>
-  </si>
-  <si>
-    <t>975c441a-75aa-4843-a88e-f57db9a75c1c</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-007] should validate Analyze Screen criteria 7</t>
-  </si>
-  <si>
-    <t>41a80f0f-98d8-4c8f-82a5-7a41cf735bf8</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-008] should validate Analyze Screen criteria 8</t>
-  </si>
-  <si>
-    <t>c286d00d-3baf-4dc2-8aed-1f7d183de37a</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-009] should validate Analyze Screen criteria 9</t>
-  </si>
-  <si>
-    <t>c8728153-19a0-414e-a39c-7e1de12e499d</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-010] should validate Analyze Screen criteria 10</t>
-  </si>
-  <si>
-    <t>411c02f3-8370-4865-86fa-b2a44a623e11</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-011] should validate Analyze Screen criteria 11</t>
-  </si>
-  <si>
-    <t>4aec447b-4c7b-45e0-b430-12497a431e5e</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-012] should validate Analyze Screen criteria 12</t>
-  </si>
-  <si>
-    <t>6efc0f6f-a044-4673-8153-201761c716e6</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-013] should validate Analyze Screen criteria 13</t>
-  </si>
-  <si>
-    <t>ed0692b2-b847-48d6-a503-b4b93de2c015</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-014] should validate Analyze Screen criteria 14</t>
-  </si>
-  <si>
-    <t>b28924ea-74f0-48b8-8c3f-ecc17a0e684c</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-015] should validate Analyze Screen criteria 15</t>
-  </si>
-  <si>
-    <t>9b5f6f72-f7fb-4cd4-bcbe-cf005cfd3e68</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-016] should validate Analyze Screen criteria 16</t>
-  </si>
-  <si>
-    <t>e96a847b-a7e9-44df-bcd3-b9c193ee903b</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-017] should validate Analyze Screen criteria 17</t>
-  </si>
-  <si>
-    <t>2465adcf-cf33-466e-a590-1f57b23d514a</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-018] should validate Analyze Screen criteria 18</t>
-  </si>
-  <si>
-    <t>21ec00ec-10e8-4c92-87b0-8b92f823c7cb</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-019] should validate Analyze Screen criteria 19</t>
-  </si>
-  <si>
-    <t>3d2cacfd-e601-4182-9b4f-69158430ca2f</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-020] should validate Analyze Screen criteria 20</t>
-  </si>
-  <si>
-    <t>86576e05-9fea-479a-bf6f-29a7264142c3</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-021] should validate Analyze Screen criteria 21</t>
-  </si>
-  <si>
-    <t>dd723c67-3203-4599-ab80-b32802c50508</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-022] should validate Analyze Screen criteria 22</t>
-  </si>
-  <si>
-    <t>62894887-9e42-4ab2-8a56-8d3f7354a3ed</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-023] should validate Analyze Screen criteria 23</t>
-  </si>
-  <si>
-    <t>d27fc482-ba1c-4861-8988-0f5739f2cb70</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-024] should validate Analyze Screen criteria 24</t>
-  </si>
-  <si>
-    <t>0ee9c3d9-3055-4fbb-b939-9f779f402e3f</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-025] should validate Analyze Screen criteria 25</t>
-  </si>
-  <si>
-    <t>60e251cd-d407-41a3-a751-eee64382fdcf</t>
+    <t>[TC-ANAL-001] Verify analyze screen requires camera access</t>
+  </si>
+  <si>
+    <t>1f5af5a2-d6b7-4216-85e4-3ae0e4a9421d</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-002] Verify analyze engine starts up correctly</t>
+  </si>
+  <si>
+    <t>99ed9f5b-8503-4284-8744-07b8ac0b13ab</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-003] Verify real-time analysis overlay renders</t>
+  </si>
+  <si>
+    <t>bee9620c-1556-4bd6-947c-a2d38e234ccb</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-004] Verify object detection bounding boxes appear</t>
+  </si>
+  <si>
+    <t>d31e5ee3-caa6-4942-9525-5bb904c2d9a4</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-005] Verify confidence score is displayed</t>
+  </si>
+  <si>
+    <t>0db406e8-a640-4b9e-bc2e-52c5ae6470dc</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-006] Verify analysis pauses when app backgrounded</t>
+  </si>
+  <si>
+    <t>69eee080-a0ab-4b2f-80e8-dca2852a6944</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-007] Verify analysis resumes when app foregrounded</t>
+  </si>
+  <si>
+    <t>dc5cd0d9-4e69-4ef0-a0c4-f3279848696e</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-008] Verify flashlight toggle during analysis</t>
+  </si>
+  <si>
+    <t>0a42c3d1-b119-43aa-b2bc-54c3fad32c7b</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-009] Verify camera flip (front/back) functionality</t>
+  </si>
+  <si>
+    <t>8fe1f583-9d64-4983-8310-3f933aa3fef3</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-010] Verify zoom functionality during analysis</t>
+  </si>
+  <si>
+    <t>4da45809-fcea-4cb3-98ff-91de91806b33</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-011] Verify analysis handles poor lighting conditions</t>
+  </si>
+  <si>
+    <t>a0dc6c1a-648b-4df7-beed-c5fee8e50c91</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-012] Verify analysis handles blurry images</t>
+  </si>
+  <si>
+    <t>f71fc55f-f595-41e7-b777-792b908e532f</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-013] Verify fast-moving object tracking</t>
+  </si>
+  <si>
+    <t>9cc00ef0-facb-431a-a880-c119fe5a5b3f</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-014] Verify multiple object detection simultaneously</t>
+  </si>
+  <si>
+    <t>2ea2ffff-27e6-41af-9657-007c64939b1f</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-015] Verify capture button snaps current frame</t>
+  </si>
+  <si>
+    <t>026c9307-e10b-4aa3-bdb0-98b267cea09f</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-016] Verify analyze history logs current session</t>
+  </si>
+  <si>
+    <t>f4194017-2b65-4e81-b48d-1671a5338323</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-017] Verify AI model version is visible</t>
+  </si>
+  <si>
+    <t>4c3c4a53-272b-4332-a61e-5c2fc414174b</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-018] Verify offline analysis mode functionality</t>
+  </si>
+  <si>
+    <t>1298bbd8-72c9-4ecf-bf01-28f8761947ca</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-019] Verify thermal/depth sensor toggle if available</t>
+  </si>
+  <si>
+    <t>38e929db-d4a5-4c0c-ac32-b049ab31bd26</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-020] Verify analysis stops gracefully on exit</t>
+  </si>
+  <si>
+    <t>8ddad6fe-d31a-414f-8ed7-aed2d034a740</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-021] Verify memory usage during prolonged analysis</t>
+  </si>
+  <si>
+    <t>01448916-6035-487f-b0c9-2708756b5398</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-022] Verify battery consumption warning</t>
+  </si>
+  <si>
+    <t>4a46d8eb-5dd7-443d-adf0-343205b027c5</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-023] Verify error when camera hardware fails</t>
+  </si>
+  <si>
+    <t>19b31f56-9f6d-4f7e-912d-98c2cc4cabcb</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-024] Verify unsupported device error message</t>
+  </si>
+  <si>
+    <t>6fef5905-0f24-4638-ab32-075f244b1d1a</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-025] Verify save analysis metadata to local DB</t>
+  </si>
+  <si>
+    <t>68f286e7-accf-4ed4-b52c-263b45a6e187</t>
   </si>
   <si>
     <t>Chatbot Screen</t>
@@ -959,154 +959,154 @@
     <t>Module: Chatbot Screen</t>
   </si>
   <si>
-    <t>[TC-CHAT-001] should validate Chatbot Screen criteria 1</t>
-  </si>
-  <si>
-    <t>1fffcd79-96fa-45aa-824f-af6bb19fafb3</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-002] should validate Chatbot Screen criteria 2</t>
-  </si>
-  <si>
-    <t>7970f73f-edc6-4223-9e76-1fccbccd258f</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-003] should validate Chatbot Screen criteria 3</t>
-  </si>
-  <si>
-    <t>5b36eb0d-e6df-4b7b-bed9-80643667b33d</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-004] should validate Chatbot Screen criteria 4</t>
-  </si>
-  <si>
-    <t>377032c2-e9eb-4ea9-a935-2b4888d58d94</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-005] should validate Chatbot Screen criteria 5</t>
-  </si>
-  <si>
-    <t>2eba234b-e364-43a3-b807-e584e07182b9</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-006] should validate Chatbot Screen criteria 6</t>
-  </si>
-  <si>
-    <t>d66d8303-0bcc-46a1-b0f0-55d56304d567</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-007] should validate Chatbot Screen criteria 7</t>
-  </si>
-  <si>
-    <t>fe59b407-7d1b-4d8e-bef6-c338e156e3dc</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-008] should validate Chatbot Screen criteria 8</t>
-  </si>
-  <si>
-    <t>288573d6-f967-42c1-b885-2bd74973c75b</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-009] should validate Chatbot Screen criteria 9</t>
-  </si>
-  <si>
-    <t>824677ee-231b-417b-9ec2-247623bd3285</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-010] should validate Chatbot Screen criteria 10</t>
-  </si>
-  <si>
-    <t>4dbfa9f4-c658-48eb-af2b-3ee6800014ba</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-011] should validate Chatbot Screen criteria 11</t>
-  </si>
-  <si>
-    <t>c8919aa5-7837-488e-90dc-d687ba49ade5</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-012] should validate Chatbot Screen criteria 12</t>
-  </si>
-  <si>
-    <t>28822af4-984f-4570-977a-76ab83175b23</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-013] should validate Chatbot Screen criteria 13</t>
-  </si>
-  <si>
-    <t>2c7106a0-4187-4718-9a86-028795421c55</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-014] should validate Chatbot Screen criteria 14</t>
-  </si>
-  <si>
-    <t>0b6c7f9e-8dd6-439b-8088-f52d4e4c1df1</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-015] should validate Chatbot Screen criteria 15</t>
-  </si>
-  <si>
-    <t>1c569d14-6180-4c5d-8fe3-208184a3c169</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-016] should validate Chatbot Screen criteria 16</t>
-  </si>
-  <si>
-    <t>1505f758-fa4f-4ca2-b8c8-f6d84ab47b8b</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-017] should validate Chatbot Screen criteria 17</t>
-  </si>
-  <si>
-    <t>90ac1937-316e-428f-a511-b9ee20b080e9</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-018] should validate Chatbot Screen criteria 18</t>
-  </si>
-  <si>
-    <t>a8a5318e-5a41-416d-b31a-4eca2a5da15c</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-019] should validate Chatbot Screen criteria 19</t>
-  </si>
-  <si>
-    <t>e7cac91f-7383-47f7-b42f-c3ba1566c165</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-020] should validate Chatbot Screen criteria 20</t>
-  </si>
-  <si>
-    <t>cc2b19bd-b52f-45ce-85b1-340c72db3cda</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-021] should validate Chatbot Screen criteria 21</t>
-  </si>
-  <si>
-    <t>61397cb8-071f-4749-adc5-1a46a83a6346</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-022] should validate Chatbot Screen criteria 22</t>
-  </si>
-  <si>
-    <t>e1c57c42-d5a7-4c71-acdf-ded0fb15b06e</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-023] should validate Chatbot Screen criteria 23</t>
-  </si>
-  <si>
-    <t>6eda1c5a-6502-4d75-a449-974aa5de2905</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-024] should validate Chatbot Screen criteria 24</t>
-  </si>
-  <si>
-    <t>1ba17a1e-3e87-4484-b548-72d23e00b2b7</t>
-  </si>
-  <si>
-    <t>[TC-CHAT-025] should validate Chatbot Screen criteria 25</t>
-  </si>
-  <si>
-    <t>5d0c1c02-d052-4dcc-ae0c-fb24bef07bdc</t>
+    <t>[TC-CHAT-001] Verify chatbot screen loads conversation history</t>
+  </si>
+  <si>
+    <t>24709bc5-12df-49e3-bbba-7a81c3033c88</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-002] Verify new message input field works</t>
+  </si>
+  <si>
+    <t>c41c0064-e33b-4610-a8d1-a7b54bf8f9d0</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-003] Verify send button disabled on empty input</t>
+  </si>
+  <si>
+    <t>bb04f8e5-57c9-4afa-9c5a-826b1dac6c6f</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-004] Verify typing indicator appears when bot processes</t>
+  </si>
+  <si>
+    <t>359fbd6d-9e06-43b4-ae69-997473c372ca</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-005] Verify bot responds with text</t>
+  </si>
+  <si>
+    <t>c867ff61-99aa-4c90-8d94-311d175c2df4</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-006] Verify bot responds with rich media (images)</t>
+  </si>
+  <si>
+    <t>18d71c99-093a-4c10-8286-1b59540236b4</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-007] Verify bot responds with action buttons</t>
+  </si>
+  <si>
+    <t>14aea5e5-1979-46f0-a7e4-1396ae06ef59</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-008] Verify clicking action button sends payload</t>
+  </si>
+  <si>
+    <t>a16a8c94-c61d-4561-86c2-43431b50e9e2</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-009] Verify timestamp on messages is correct</t>
+  </si>
+  <si>
+    <t>9fed90b6-e9d2-4d31-b551-2e830a4eea2d</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-010] Verify user messages align right</t>
+  </si>
+  <si>
+    <t>1ed0090f-9468-44c3-8c7d-a2b5c72c37b0</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-011] Verify bot messages align left</t>
+  </si>
+  <si>
+    <t>4acb20de-f1da-4570-b18f-4f3fcd8ec370</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-012] Verify scroll to bottom on new message</t>
+  </si>
+  <si>
+    <t>a4995f22-daf3-42a0-b4b4-d9849ad8bacb</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-013] Verify pull down loads older messages</t>
+  </si>
+  <si>
+    <t>a85c9c5e-8379-413a-90a4-6c39334cf91f</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-014] Verify quick reply chips disappear after use</t>
+  </si>
+  <si>
+    <t>5202663d-1b57-4b02-84e2-ad28f04619d1</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-015] Verify voice input to text translation</t>
+  </si>
+  <si>
+    <t>4a9aeb4b-2125-4eab-9b5c-27401559257d</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-016] Verify clear chat history functionality</t>
+  </si>
+  <si>
+    <t>3dcd46f4-c013-4cff-a4fe-d18c697d8992</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-017] Verify export chat transcript</t>
+  </si>
+  <si>
+    <t>3a2556d4-4d75-431f-bd31-3d7ad2e237c7</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-018] Verify chatbot handles network disconnect</t>
+  </si>
+  <si>
+    <t>caa1cef1-02de-426c-9151-b381255da1e6</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-019] Verify chatbot handles session timeout</t>
+  </si>
+  <si>
+    <t>29b969f7-3244-4016-86b7-7b656245a581</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-020] Verify swear word filter on user input</t>
+  </si>
+  <si>
+    <t>7b3383fd-00b2-4bf3-8302-fc86186a1e01</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-021] Verify bot fallback message on unknown intent</t>
+  </si>
+  <si>
+    <t>c8661735-1830-4ec2-b2df-241972f5bb40</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-022] Verify rating prompt after conversation</t>
+  </si>
+  <si>
+    <t>d708de5c-43c6-4e8c-9eea-fb0bb6dd97eb</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-023] Verify minimize chatbot widget</t>
+  </si>
+  <si>
+    <t>2ead2051-85f6-485c-a1f4-f3e1fedac77b</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-024] Verify unread message badge on widget</t>
+  </si>
+  <si>
+    <t>26c726e0-bbcc-46e4-a495-138dd6a009d8</t>
+  </si>
+  <si>
+    <t>[TC-CHAT-025] Verify copy message text to clipboard</t>
+  </si>
+  <si>
+    <t>53a61a1f-9aa2-4e8e-8d78-df40ef85fadf</t>
   </si>
   <si>
     <t>History Screen</t>
@@ -1115,94 +1115,94 @@
     <t>Module: History Screen</t>
   </si>
   <si>
-    <t>[TC-HIST-001] should validate History Screen criteria 1</t>
-  </si>
-  <si>
-    <t>c86a07c5-2500-4706-b1e9-d4616185fb4a</t>
-  </si>
-  <si>
-    <t>[TC-HIST-002] should validate History Screen criteria 2</t>
-  </si>
-  <si>
-    <t>5b821ecd-ee1d-4b14-86ea-66ce63b32dc9</t>
-  </si>
-  <si>
-    <t>[TC-HIST-003] should validate History Screen criteria 3</t>
-  </si>
-  <si>
-    <t>ffa83882-789a-4eec-9cc1-b72cd7e89f90</t>
-  </si>
-  <si>
-    <t>[TC-HIST-004] should validate History Screen criteria 4</t>
-  </si>
-  <si>
-    <t>6d45e0aa-866c-43ac-b67e-748e60d7f568</t>
-  </si>
-  <si>
-    <t>[TC-HIST-005] should validate History Screen criteria 5</t>
-  </si>
-  <si>
-    <t>dee16a2c-b4ff-4a3f-8a23-aaee0d4cbf97</t>
-  </si>
-  <si>
-    <t>[TC-HIST-006] should validate History Screen criteria 6</t>
-  </si>
-  <si>
-    <t>cafa3594-f9a9-410a-b3f6-d48f39053c22</t>
-  </si>
-  <si>
-    <t>[TC-HIST-007] should validate History Screen criteria 7</t>
-  </si>
-  <si>
-    <t>5242893b-2a21-4e39-af73-3c3d00fb627a</t>
-  </si>
-  <si>
-    <t>[TC-HIST-008] should validate History Screen criteria 8</t>
-  </si>
-  <si>
-    <t>9bf3d95a-0a81-40d1-929b-00667ba32cb0</t>
-  </si>
-  <si>
-    <t>[TC-HIST-009] should validate History Screen criteria 9</t>
-  </si>
-  <si>
-    <t>1e52e092-74ad-4cc5-a367-b01d5000797f</t>
-  </si>
-  <si>
-    <t>[TC-HIST-010] should validate History Screen criteria 10</t>
-  </si>
-  <si>
-    <t>697f21a3-a100-411c-bd65-d140671d1f10</t>
-  </si>
-  <si>
-    <t>[TC-HIST-011] should validate History Screen criteria 11</t>
-  </si>
-  <si>
-    <t>7522dc2a-5e76-4f3a-9cc2-8403136b18d8</t>
-  </si>
-  <si>
-    <t>[TC-HIST-012] should validate History Screen criteria 12</t>
-  </si>
-  <si>
-    <t>cd40f977-3c90-42a3-9e9e-e82e904ff2b6</t>
-  </si>
-  <si>
-    <t>[TC-HIST-013] should validate History Screen criteria 13</t>
-  </si>
-  <si>
-    <t>039e0578-01b8-43b5-8f1f-6552af123698</t>
-  </si>
-  <si>
-    <t>[TC-HIST-014] should validate History Screen criteria 14</t>
-  </si>
-  <si>
-    <t>7fdcf37c-f1e4-48ca-84c4-c613e8b94f2c</t>
-  </si>
-  <si>
-    <t>[TC-HIST-015] should validate History Screen criteria 15</t>
-  </si>
-  <si>
-    <t>fada18f3-fcb3-4bc4-8596-128c16a5212c</t>
+    <t>[TC-HIST-001] Verify history list loads from local DB</t>
+  </si>
+  <si>
+    <t>8a3f7f96-a862-4acf-9300-4e378a79e28d</t>
+  </si>
+  <si>
+    <t>[TC-HIST-002] Verify chronological sorting of history items</t>
+  </si>
+  <si>
+    <t>7979fffb-3a89-4694-b589-f5b3e1dc203d</t>
+  </si>
+  <si>
+    <t>[TC-HIST-003] Verify grouping history by date</t>
+  </si>
+  <si>
+    <t>86415dcf-b437-4737-81ac-06eb8431b3e1</t>
+  </si>
+  <si>
+    <t>[TC-HIST-004] Verify pull-to-refresh syncs cloud history</t>
+  </si>
+  <si>
+    <t>51754a18-8d54-41dc-ada4-24c714a62d6a</t>
+  </si>
+  <si>
+    <t>[TC-HIST-005] Verify clicking history item opens details</t>
+  </si>
+  <si>
+    <t>c948ac9a-35c7-4b8e-805c-999e7cf3d055</t>
+  </si>
+  <si>
+    <t>[TC-HIST-006] Verify delete individual history item</t>
+  </si>
+  <si>
+    <t>b02f7211-1b4e-4b99-b6f0-bae32d635e17</t>
+  </si>
+  <si>
+    <t>[TC-HIST-007] Verify swipe-to-delete history item</t>
+  </si>
+  <si>
+    <t>c57dfc86-2ce1-48c4-8fc4-8fa9ae5a0b27</t>
+  </si>
+  <si>
+    <t>[TC-HIST-008] Verify bulk delete multiple history items</t>
+  </si>
+  <si>
+    <t>0863b4b3-a291-4eff-9213-8afa7c5b03e6</t>
+  </si>
+  <si>
+    <t>[TC-HIST-009] Verify clear all history opens warning</t>
+  </si>
+  <si>
+    <t>0adc9d7d-9f03-4785-ba49-13e95c702e5d</t>
+  </si>
+  <si>
+    <t>[TC-HIST-010] Verify search history by keyword</t>
+  </si>
+  <si>
+    <t>10777c1d-e60a-4536-b22a-f677bffa96de</t>
+  </si>
+  <si>
+    <t>[TC-HIST-011] Verify filter history by category</t>
+  </si>
+  <si>
+    <t>6ec7e21d-bbb0-47b5-95c7-e65f6843f697</t>
+  </si>
+  <si>
+    <t>[TC-HIST-012] Verify filter history by date range</t>
+  </si>
+  <si>
+    <t>b4953ab4-692f-4dab-a750-cd08e947c118</t>
+  </si>
+  <si>
+    <t>[TC-HIST-013] Verify empty state illustration when no history</t>
+  </si>
+  <si>
+    <t>0a7ffe2c-a34b-4c17-a456-d1d79ec5e4ae</t>
+  </si>
+  <si>
+    <t>[TC-HIST-014] Verify pagination/infinite scroll on large history</t>
+  </si>
+  <si>
+    <t>500757d8-2dbb-4b39-885b-152e3fac9ca1</t>
+  </si>
+  <si>
+    <t>[TC-HIST-015] Verify export history to CSV</t>
+  </si>
+  <si>
+    <t>d4f31119-7a09-4b59-9a7b-21a68e18e8c9</t>
   </si>
   <si>
     <t>Capture Screen</t>
@@ -1211,94 +1211,94 @@
     <t>Module: Capture Screen</t>
   </si>
   <si>
-    <t>[TC-CAPT-001] should validate Capture Screen criteria 1</t>
-  </si>
-  <si>
-    <t>83b8ef7d-0ad6-46f2-aefb-8bde5691f7ea</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-002] should validate Capture Screen criteria 2</t>
-  </si>
-  <si>
-    <t>234d5426-5544-41df-aa6a-d018e5b9d6e3</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-003] should validate Capture Screen criteria 3</t>
-  </si>
-  <si>
-    <t>9883e2e5-95cc-43d1-9074-e12a63c966e8</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-004] should validate Capture Screen criteria 4</t>
-  </si>
-  <si>
-    <t>3f66f23e-1c7a-46cd-9c17-5857fd8ab8e6</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-005] should validate Capture Screen criteria 5</t>
-  </si>
-  <si>
-    <t>8cb1e807-bb3c-4f84-a8ed-733a8b879d02</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-006] should validate Capture Screen criteria 6</t>
-  </si>
-  <si>
-    <t>bcd598d8-3708-403d-9630-a2dbed31d7de</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-007] should validate Capture Screen criteria 7</t>
-  </si>
-  <si>
-    <t>4ce324e6-fb10-43fd-8913-b7d215c4484a</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-008] should validate Capture Screen criteria 8</t>
-  </si>
-  <si>
-    <t>a12c246f-744b-4c7a-8b5d-0e2f35ae03c8</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-009] should validate Capture Screen criteria 9</t>
-  </si>
-  <si>
-    <t>33b4284f-6022-4699-af54-59f252c97bc3</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-010] should validate Capture Screen criteria 10</t>
-  </si>
-  <si>
-    <t>92f49427-fc09-414d-b69e-dcdb04d5e233</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-011] should validate Capture Screen criteria 11</t>
-  </si>
-  <si>
-    <t>42715ba1-12b0-42a8-89b6-f82be049ee95</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-012] should validate Capture Screen criteria 12</t>
-  </si>
-  <si>
-    <t>ca135d92-13bc-49bc-9e15-65c6cb41df4e</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-013] should validate Capture Screen criteria 13</t>
-  </si>
-  <si>
-    <t>b01ebc94-15e3-4cee-8c19-9d1c6e382c00</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-014] should validate Capture Screen criteria 14</t>
-  </si>
-  <si>
-    <t>0824f92c-85e5-49a2-94e8-afaf16201abf</t>
-  </si>
-  <si>
-    <t>[TC-CAPT-015] should validate Capture Screen criteria 15</t>
-  </si>
-  <si>
-    <t>1bda63a6-a2c1-4d99-9496-b8411839a199</t>
+    <t>[TC-CAPT-001] Verify capture screen initializes camera quickly</t>
+  </si>
+  <si>
+    <t>2a4c1a30-f112-404a-a912-b65bbbc027c3</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-002] Verify grid overlay toggle</t>
+  </si>
+  <si>
+    <t>555624c1-0cd4-4ad9-99a6-5e43a979ec00</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-003] Verify aspect ratio toggle (1:1, 4:3, 16:9)</t>
+  </si>
+  <si>
+    <t>38674711-3475-4271-a0f2-3015df835ae1</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-004] Verify timer functionality (3s, 10s)</t>
+  </si>
+  <si>
+    <t>a4c4bf57-c35b-44e9-9412-92ed954beed0</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-005] Verify flash modes (Auto, On, Off)</t>
+  </si>
+  <si>
+    <t>5246a0de-b287-4c1c-aebd-115f9e137daa</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-006] Verify HDR toggle functionality</t>
+  </si>
+  <si>
+    <t>e89f846d-5f66-4f24-a1f8-cf4834890237</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-007] Verify shutter button snaps photo</t>
+  </si>
+  <si>
+    <t>e97e86d5-ba6e-40ba-b72a-c09027a278d8</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-008] Verify burst mode on holding shutter</t>
+  </si>
+  <si>
+    <t>7ac630cf-c819-433f-a082-ee5a168241aa</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-009] Verify video recording starts on long press</t>
+  </si>
+  <si>
+    <t>d19807da-eeaa-4e42-a1e3-93b5e4b5f11e</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-010] Verify preview thumbnail updates after capture</t>
+  </si>
+  <si>
+    <t>f3c06f63-ee0a-4e5c-9c74-482429deb651</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-011] Verify clicking thumbnail opens gallery</t>
+  </si>
+  <si>
+    <t>e790fb7a-180d-4b8c-b350-0629cf1210ff</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-012] Verify auto-focus on tap</t>
+  </si>
+  <si>
+    <t>e93f9616-b505-419e-afe4-d0a8f32f9dd3</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-013] Verify exposure slider adjustment</t>
+  </si>
+  <si>
+    <t>882a2d87-655b-4fbb-8693-c937b86a0e52</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-014] Verify capture fails gracefully if storage full</t>
+  </si>
+  <si>
+    <t>e0c585ef-32e8-4e8a-ac8c-709011244f94</t>
+  </si>
+  <si>
+    <t>[TC-CAPT-015] Verify location tagging (EXIF) on capture</t>
+  </si>
+  <si>
+    <t>c6a81bb8-65c6-4c71-b186-d61b98f31244</t>
   </si>
   <si>
     <t>Match Checker Screen</t>
@@ -1307,94 +1307,94 @@
     <t>Module: Match Checker Screen</t>
   </si>
   <si>
-    <t>[TC-MATC-001] should validate Match Checker Screen criteria 1</t>
-  </si>
-  <si>
-    <t>bd00ad02-b078-4075-8eea-552bfe7d93bb</t>
-  </si>
-  <si>
-    <t>[TC-MATC-002] should validate Match Checker Screen criteria 2</t>
-  </si>
-  <si>
-    <t>445e061b-97c8-43bb-8414-c99037c2b821</t>
-  </si>
-  <si>
-    <t>[TC-MATC-003] should validate Match Checker Screen criteria 3</t>
-  </si>
-  <si>
-    <t>0fa030d6-9d9c-41fa-ab3a-4baec75fec40</t>
-  </si>
-  <si>
-    <t>[TC-MATC-004] should validate Match Checker Screen criteria 4</t>
-  </si>
-  <si>
-    <t>c2982f1c-421c-452b-8984-c3e95a81adef</t>
-  </si>
-  <si>
-    <t>[TC-MATC-005] should validate Match Checker Screen criteria 5</t>
-  </si>
-  <si>
-    <t>b6f5ee6e-5736-4675-8da8-724f2aa1bb49</t>
-  </si>
-  <si>
-    <t>[TC-MATC-006] should validate Match Checker Screen criteria 6</t>
-  </si>
-  <si>
-    <t>f8ee57e7-e902-477d-b063-a4c6bc5da20f</t>
-  </si>
-  <si>
-    <t>[TC-MATC-007] should validate Match Checker Screen criteria 7</t>
-  </si>
-  <si>
-    <t>46231994-6a79-464c-b22e-5a6625f3c2bb</t>
-  </si>
-  <si>
-    <t>[TC-MATC-008] should validate Match Checker Screen criteria 8</t>
-  </si>
-  <si>
-    <t>8b53a458-4c21-4783-94cc-65cadbe9f0cd</t>
-  </si>
-  <si>
-    <t>[TC-MATC-009] should validate Match Checker Screen criteria 9</t>
-  </si>
-  <si>
-    <t>fbef4cad-19e2-4d06-90d3-718acbec3b33</t>
-  </si>
-  <si>
-    <t>[TC-MATC-010] should validate Match Checker Screen criteria 10</t>
-  </si>
-  <si>
-    <t>458ce84f-f8e2-460a-b229-b55d97af50a4</t>
-  </si>
-  <si>
-    <t>[TC-MATC-011] should validate Match Checker Screen criteria 11</t>
-  </si>
-  <si>
-    <t>a4b77fbe-0d75-48e0-bfab-dd77c17636df</t>
-  </si>
-  <si>
-    <t>[TC-MATC-012] should validate Match Checker Screen criteria 12</t>
-  </si>
-  <si>
-    <t>239803cb-3a67-4e27-9ec0-3c904af0dd54</t>
-  </si>
-  <si>
-    <t>[TC-MATC-013] should validate Match Checker Screen criteria 13</t>
-  </si>
-  <si>
-    <t>11356eb8-96cb-4ea5-8099-59fcd445b0c2</t>
-  </si>
-  <si>
-    <t>[TC-MATC-014] should validate Match Checker Screen criteria 14</t>
-  </si>
-  <si>
-    <t>b5fba818-fb66-4ce9-8c16-8eacba93af9d</t>
-  </si>
-  <si>
-    <t>[TC-MATC-015] should validate Match Checker Screen criteria 15</t>
-  </si>
-  <si>
-    <t>2edef86d-32b5-458a-b869-f791425e0991</t>
+    <t>[TC-MATC-001] Verify match checker takes two inputs</t>
+  </si>
+  <si>
+    <t>35ad9ac6-c280-48cc-aa90-ce5d14881c80</t>
+  </si>
+  <si>
+    <t>[TC-MATC-002] Verify input A selection from gallery</t>
+  </si>
+  <si>
+    <t>02668124-3a9b-4f0d-b761-1df36424e8fd</t>
+  </si>
+  <si>
+    <t>[TC-MATC-003] Verify input B selection from camera</t>
+  </si>
+  <si>
+    <t>5e9b0de3-8226-4b12-8060-65167438e9b1</t>
+  </si>
+  <si>
+    <t>[TC-MATC-004] Verify run match algorithm button</t>
+  </si>
+  <si>
+    <t>6cd5dc53-52e9-4f04-9f73-ff36aaa8a8fe</t>
+  </si>
+  <si>
+    <t>[TC-MATC-005] Verify progress bar during matching</t>
+  </si>
+  <si>
+    <t>4392da79-9592-49eb-bcf1-6f296f5dc3ac</t>
+  </si>
+  <si>
+    <t>[TC-MATC-006] Verify match percentage score is displayed</t>
+  </si>
+  <si>
+    <t>6dd1b5c2-e0e7-4271-8314-334936e8abd1</t>
+  </si>
+  <si>
+    <t>[TC-MATC-007] Verify detailed match breakdown chart</t>
+  </si>
+  <si>
+    <t>7d767891-d84c-408e-9f0b-7c698b74cb87</t>
+  </si>
+  <si>
+    <t>[TC-MATC-008] Verify matching highlights differences</t>
+  </si>
+  <si>
+    <t>e8d43ef5-3db8-4aff-8b10-d7149b0054ec</t>
+  </si>
+  <si>
+    <t>[TC-MATC-009] Verify matching highlights similarities</t>
+  </si>
+  <si>
+    <t>e215e356-3f66-4528-a36c-98175f1f5329</t>
+  </si>
+  <si>
+    <t>[TC-MATC-010] Verify save match result functionality</t>
+  </si>
+  <si>
+    <t>e7b9a580-e7b4-41d1-b4f8-c2f5adc4c128</t>
+  </si>
+  <si>
+    <t>[TC-MATC-011] Verify share match result via native sheet</t>
+  </si>
+  <si>
+    <t>c85acf98-b695-42fc-8b0c-57079a410394</t>
+  </si>
+  <si>
+    <t>[TC-MATC-012] Verify error when inputs are incompatible</t>
+  </si>
+  <si>
+    <t>05a2f30e-8ded-41a1-a706-d3a68547a3a2</t>
+  </si>
+  <si>
+    <t>[TC-MATC-013] Verify 3D model matching view</t>
+  </si>
+  <si>
+    <t>6bfe6fe2-79c1-490b-864a-505da08ae381</t>
+  </si>
+  <si>
+    <t>[TC-MATC-014] Verify AR overlay of matched items</t>
+  </si>
+  <si>
+    <t>35a5e3f1-0a1d-41e2-8d46-c4f3fb6a6441</t>
+  </si>
+  <si>
+    <t>[TC-MATC-015] Verify reset match checker clears inputs</t>
+  </si>
+  <si>
+    <t>14e14003-118e-4960-bdb3-9460447de095</t>
   </si>
   <si>
     <t>Shop Screen</t>
@@ -1403,94 +1403,94 @@
     <t>Module: Shop Screen</t>
   </si>
   <si>
-    <t>[TC-SHOP-001] should validate Shop Screen criteria 1</t>
-  </si>
-  <si>
-    <t>a5ac2bbc-083e-4d1f-a26a-d4d133c3c97b</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-002] should validate Shop Screen criteria 2</t>
-  </si>
-  <si>
-    <t>34548003-e0a1-42d1-a5a9-40368ed9b4a9</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-003] should validate Shop Screen criteria 3</t>
-  </si>
-  <si>
-    <t>52c653d9-ecf4-4045-8dbd-1afa5a7f88f4</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-004] should validate Shop Screen criteria 4</t>
-  </si>
-  <si>
-    <t>e6bfe416-cfe7-498c-a31b-1cc0841b5662</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-005] should validate Shop Screen criteria 5</t>
-  </si>
-  <si>
-    <t>7a761a20-1dac-4458-8ac9-bf431fe8a887</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-006] should validate Shop Screen criteria 6</t>
-  </si>
-  <si>
-    <t>3345d3e6-b26d-4fd2-9064-8638ab9885cc</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-007] should validate Shop Screen criteria 7</t>
-  </si>
-  <si>
-    <t>e65aa833-11f0-4f0d-a4f3-8876938b1b17</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-008] should validate Shop Screen criteria 8</t>
-  </si>
-  <si>
-    <t>b38fe240-7dc2-436b-929a-d40a1a5ec19d</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-009] should validate Shop Screen criteria 9</t>
-  </si>
-  <si>
-    <t>2a9e012f-4e01-4417-9d3d-f32c42d266c3</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-010] should validate Shop Screen criteria 10</t>
-  </si>
-  <si>
-    <t>0df1ba89-b993-4162-bb76-4d04ca41f0a0</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-011] should validate Shop Screen criteria 11</t>
-  </si>
-  <si>
-    <t>5fadd597-1b55-490a-b6bb-5dc5f9e92182</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-012] should validate Shop Screen criteria 12</t>
-  </si>
-  <si>
-    <t>c4cd8be7-09f3-4a6b-9492-2743840aaaa3</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-013] should validate Shop Screen criteria 13</t>
-  </si>
-  <si>
-    <t>c38db9cf-d78e-44d8-9a6c-3f6b871f6312</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-014] should validate Shop Screen criteria 14</t>
-  </si>
-  <si>
-    <t>05dd768a-1c2d-4372-8f7a-3303d52cf3b0</t>
-  </si>
-  <si>
-    <t>[TC-SHOP-015] should validate Shop Screen criteria 15</t>
-  </si>
-  <si>
-    <t>c54c6e4d-ccd3-4b13-b128-a533798aac59</t>
+    <t>[TC-SHOP-001] Verify shop catalog loads products</t>
+  </si>
+  <si>
+    <t>1555d47f-561c-4f2f-b414-a09a02274a19</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-002] Verify product categories horizontal scroll</t>
+  </si>
+  <si>
+    <t>371e4975-5aad-4f8b-a104-81c939e46b5d</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-003] Verify product card displays price and image</t>
+  </si>
+  <si>
+    <t>8362b735-eeca-4fd4-8a88-f065996cf65f</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-004] Verify clicking product opens details page</t>
+  </si>
+  <si>
+    <t>ca604d2b-a457-4a0a-be2f-acc5a4021ec4</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-005] Verify add to cart button animates</t>
+  </si>
+  <si>
+    <t>ac82fafe-ba56-4089-a1f0-3fb5f2cbaf35</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-006] Verify cart badge increments</t>
+  </si>
+  <si>
+    <t>bd46bbd7-a817-4f13-91b4-b9a6edfa0779</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-007] Verify wishlist heart toggle</t>
+  </si>
+  <si>
+    <t>97ad321e-26d3-4834-8667-50cbfdcbf46f</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-008] Verify sort by price (Low to High)</t>
+  </si>
+  <si>
+    <t>914ffb2b-d5ca-43e0-b9a7-49b4f1616bb0</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-009] Verify filter by size and color</t>
+  </si>
+  <si>
+    <t>79cc0e55-df3e-4a3f-8b64-30553edbbefd</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-010] Verify search products by name</t>
+  </si>
+  <si>
+    <t>bd0b7dde-139a-46a2-89bf-377418974719</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-011] Verify out of stock items are grayed out</t>
+  </si>
+  <si>
+    <t>6ca5e39c-864b-4552-ad87-e890cf0d4a75</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-012] Verify product image carousel swipe</t>
+  </si>
+  <si>
+    <t>bfcb3aa1-8b9c-4344-98ca-a6c07081d1dd</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-013] Verify reading product reviews</t>
+  </si>
+  <si>
+    <t>406ce81a-f9d1-4036-84cc-07c3c510be81</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-014] Verify writing a product review</t>
+  </si>
+  <si>
+    <t>11034a76-8a17-431a-9819-aca2e6dc3ed9</t>
+  </si>
+  <si>
+    <t>[TC-SHOP-015] Verify related products section</t>
+  </si>
+  <si>
+    <t>565f39d7-1848-4770-b83f-ce658f795e19</t>
   </si>
   <si>
     <t>Recommended Colors Screen</t>
@@ -1499,94 +1499,94 @@
     <t>Module: Recommended Colors Screen</t>
   </si>
   <si>
-    <t>[TC-RECO-001] should validate Recommended Colors Screen criteria 1</t>
-  </si>
-  <si>
-    <t>48aefb9b-eb80-46ee-8f8e-bb6ce257b0bc</t>
-  </si>
-  <si>
-    <t>[TC-RECO-002] should validate Recommended Colors Screen criteria 2</t>
-  </si>
-  <si>
-    <t>55db934a-7d6a-4832-bddf-4924751e4230</t>
-  </si>
-  <si>
-    <t>[TC-RECO-003] should validate Recommended Colors Screen criteria 3</t>
-  </si>
-  <si>
-    <t>edc8c5b8-5c0c-498f-a1b0-7f8cbd4d6972</t>
-  </si>
-  <si>
-    <t>[TC-RECO-004] should validate Recommended Colors Screen criteria 4</t>
-  </si>
-  <si>
-    <t>2b2f1252-50c3-4a46-a8a3-d9dcb4397ef1</t>
-  </si>
-  <si>
-    <t>[TC-RECO-005] should validate Recommended Colors Screen criteria 5</t>
-  </si>
-  <si>
-    <t>7a9355e6-89b4-4f9a-bb21-130d4d295ba7</t>
-  </si>
-  <si>
-    <t>[TC-RECO-006] should validate Recommended Colors Screen criteria 6</t>
-  </si>
-  <si>
-    <t>4cca2379-0bd7-4179-8e24-e8eda3902729</t>
-  </si>
-  <si>
-    <t>[TC-RECO-007] should validate Recommended Colors Screen criteria 7</t>
-  </si>
-  <si>
-    <t>424cc6fd-c5d0-43d5-a27b-9e65e1cd88fd</t>
-  </si>
-  <si>
-    <t>[TC-RECO-008] should validate Recommended Colors Screen criteria 8</t>
-  </si>
-  <si>
-    <t>443f820b-22ae-4e2c-91d2-bf950a56c86a</t>
-  </si>
-  <si>
-    <t>[TC-RECO-009] should validate Recommended Colors Screen criteria 9</t>
-  </si>
-  <si>
-    <t>c8bceaf9-7fb0-4c1c-a4e4-59b3738f723e</t>
-  </si>
-  <si>
-    <t>[TC-RECO-010] should validate Recommended Colors Screen criteria 10</t>
-  </si>
-  <si>
-    <t>5148a4b2-8d3a-49e6-b36c-688972d22331</t>
-  </si>
-  <si>
-    <t>[TC-RECO-011] should validate Recommended Colors Screen criteria 11</t>
-  </si>
-  <si>
-    <t>aa287aa8-13ad-4567-8246-c35945712093</t>
-  </si>
-  <si>
-    <t>[TC-RECO-012] should validate Recommended Colors Screen criteria 12</t>
-  </si>
-  <si>
-    <t>13e904a9-10ee-47d6-88e0-667ba25bd92b</t>
-  </si>
-  <si>
-    <t>[TC-RECO-013] should validate Recommended Colors Screen criteria 13</t>
-  </si>
-  <si>
-    <t>95473060-2a16-46c4-a7ec-27bf5a3d6ac5</t>
-  </si>
-  <si>
-    <t>[TC-RECO-014] should validate Recommended Colors Screen criteria 14</t>
-  </si>
-  <si>
-    <t>d952121c-ccbc-41b3-9607-8e3898455b47</t>
-  </si>
-  <si>
-    <t>[TC-RECO-015] should validate Recommended Colors Screen criteria 15</t>
-  </si>
-  <si>
-    <t>6b6a0aa7-0b38-4da7-a1f3-187e18c89f9d</t>
+    <t>[TC-RECO-001] Verify color palette generation based on profile</t>
+  </si>
+  <si>
+    <t>b40c2b77-1fb4-462a-8471-678c2fc8e45e</t>
+  </si>
+  <si>
+    <t>[TC-RECO-002] Verify primary color hex code is visible</t>
+  </si>
+  <si>
+    <t>e2627ef1-8236-44ce-b21f-894646fadbb0</t>
+  </si>
+  <si>
+    <t>[TC-RECO-003] Verify secondary color hex code is visible</t>
+  </si>
+  <si>
+    <t>beab3392-8a8f-4f0c-93de-80c7af7fda42</t>
+  </si>
+  <si>
+    <t>[TC-RECO-004] Verify accent color hex code is visible</t>
+  </si>
+  <si>
+    <t>ef3b1e6f-ab89-444e-ad2f-ce990dc1e2cc</t>
+  </si>
+  <si>
+    <t>[TC-RECO-005] Verify tap to copy hex code to clipboard</t>
+  </si>
+  <si>
+    <t>22e76d14-486c-4614-a29a-5e92c19d4f4f</t>
+  </si>
+  <si>
+    <t>[TC-RECO-006] Verify color blind simulation view</t>
+  </si>
+  <si>
+    <t>602755a9-5c49-4d46-9abb-a74a434be7c3</t>
+  </si>
+  <si>
+    <t>[TC-RECO-007] Verify save palette to favorites</t>
+  </si>
+  <si>
+    <t>92c91f0a-e0a6-4d72-8262-490a6b8bc4ba</t>
+  </si>
+  <si>
+    <t>[TC-RECO-008] Verify share palette as image</t>
+  </si>
+  <si>
+    <t>6384439b-acda-427c-a379-e9ff1c72bc52</t>
+  </si>
+  <si>
+    <t>[TC-RECO-009] Verify applying palette to app theme preview</t>
+  </si>
+  <si>
+    <t>18b3c8e6-dd8f-4807-8acc-f80a81a4549c</t>
+  </si>
+  <si>
+    <t>[TC-RECO-010] Verify color harmony rule selection (Analogous)</t>
+  </si>
+  <si>
+    <t>938f3669-9658-46c1-94d3-8c34678baa94</t>
+  </si>
+  <si>
+    <t>[TC-RECO-011] Verify color harmony rule selection (Complementary)</t>
+  </si>
+  <si>
+    <t>882224c2-9898-4125-a34b-e41a60afb644</t>
+  </si>
+  <si>
+    <t>[TC-RECO-012] Verify extract colors from uploaded image</t>
+  </si>
+  <si>
+    <t>89ac4b0f-0b56-445a-af63-5989aa65cf06</t>
+  </si>
+  <si>
+    <t>[TC-RECO-013] Verify contrast ratio checker passes</t>
+  </si>
+  <si>
+    <t>65c0465a-2317-4919-90ba-586f96570aea</t>
+  </si>
+  <si>
+    <t>[TC-RECO-014] Verify seasonal color recommendations</t>
+  </si>
+  <si>
+    <t>80185592-8312-4a29-8f51-677221cce4fe</t>
+  </si>
+  <si>
+    <t>[TC-RECO-015] Verify trending colors API integration</t>
+  </si>
+  <si>
+    <t>0e500df2-6fee-434d-bd27-08cfa0fb080d</t>
   </si>
   <si>
     <t>Analysis Result Screen</t>
@@ -1595,94 +1595,94 @@
     <t>Module: Analysis Result Screen</t>
   </si>
   <si>
-    <t>[TC-ANAL-001] should validate Analysis Result Screen criteria 1</t>
-  </si>
-  <si>
-    <t>89cc5f47-edb4-445d-80f2-7f845d493651</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-002] should validate Analysis Result Screen criteria 2</t>
-  </si>
-  <si>
-    <t>7fd65865-497d-4e94-890a-12729c06606e</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-003] should validate Analysis Result Screen criteria 3</t>
-  </si>
-  <si>
-    <t>279a6d5b-f8d6-4cd3-951d-9068f91cf01a</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-004] should validate Analysis Result Screen criteria 4</t>
-  </si>
-  <si>
-    <t>6623d329-34a5-4eae-8fd5-054a26975b69</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-005] should validate Analysis Result Screen criteria 5</t>
-  </si>
-  <si>
-    <t>f74872d8-2516-43c0-9065-84da7a707ebe</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-006] should validate Analysis Result Screen criteria 6</t>
-  </si>
-  <si>
-    <t>d56be115-a563-447d-8d21-eff3123c06c3</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-007] should validate Analysis Result Screen criteria 7</t>
-  </si>
-  <si>
-    <t>12af10c4-6cb3-49a1-99e2-8849181ead6d</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-008] should validate Analysis Result Screen criteria 8</t>
-  </si>
-  <si>
-    <t>92bd3150-7d3b-4b99-a6ec-c2baa5750859</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-009] should validate Analysis Result Screen criteria 9</t>
-  </si>
-  <si>
-    <t>d2a7e078-1bbb-4f3c-802f-dd569a8c8e22</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-010] should validate Analysis Result Screen criteria 10</t>
-  </si>
-  <si>
-    <t>88048ec7-4d82-4cb7-9eab-a561bffdcf10</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-011] should validate Analysis Result Screen criteria 11</t>
-  </si>
-  <si>
-    <t>a00d5cd5-2bed-4989-b7b1-874203b1681f</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-012] should validate Analysis Result Screen criteria 12</t>
-  </si>
-  <si>
-    <t>8589ff55-44aa-4c18-a42c-f79b2140d54e</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-013] should validate Analysis Result Screen criteria 13</t>
-  </si>
-  <si>
-    <t>9b3cd625-b8b3-4758-85d4-882936881051</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-014] should validate Analysis Result Screen criteria 14</t>
-  </si>
-  <si>
-    <t>1f7a8890-387b-450d-9399-53b0dad18599</t>
-  </si>
-  <si>
-    <t>[TC-ANAL-015] should validate Analysis Result Screen criteria 15</t>
-  </si>
-  <si>
-    <t>c06e1af7-7244-4d10-8c09-27de069bbe67</t>
+    <t>[TC-ANAL-001] Verify result screen displays source image</t>
+  </si>
+  <si>
+    <t>6ce0b9ed-2563-4b91-b9f7-520ce548ce60</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-002] Verify main detected entity title</t>
+  </si>
+  <si>
+    <t>275eb53f-1667-4ff9-9a25-d665813d0d34</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-003] Verify confidence score gauge chart</t>
+  </si>
+  <si>
+    <t>b55d889e-6920-463b-9a20-efab1c32966b</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-004] Verify detailed attributes list</t>
+  </si>
+  <si>
+    <t>abc99044-d3d4-4c52-9694-44bf0fa0ab19</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-005] Verify actionable recommendations based on result</t>
+  </si>
+  <si>
+    <t>384958a3-af01-460a-9aa3-e6d9e18ca538</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-006] Verify export result to PDF</t>
+  </si>
+  <si>
+    <t>419355ff-4c0d-440b-a17b-3f3ee60cb5b0</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-007] Verify share result link generation</t>
+  </si>
+  <si>
+    <t>1bbd9dc3-873d-4955-860b-f8cbab716df5</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-008] Verify flag result as incorrect (Feedback loop)</t>
+  </si>
+  <si>
+    <t>f7a8cb00-b303-4c34-90b3-2488930323f1</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-009] Verify related articles/knowledge base links</t>
+  </si>
+  <si>
+    <t>6f94f04f-a007-4cbd-a483-ee2fbbd62f25</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-010] Verify 3D visualization of result if applicable</t>
+  </si>
+  <si>
+    <t>d8eaaa23-1dda-44dc-9dcf-00905b86106a</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-011] Verify compare with previous results</t>
+  </si>
+  <si>
+    <t>0d5504c0-4b3e-4287-ac14-26088caa6eab</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-012] Verify save to specific project folder</t>
+  </si>
+  <si>
+    <t>34be89d3-381b-4bdf-b005-362415e8de22</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-013] Verify delete result from database</t>
+  </si>
+  <si>
+    <t>156fbcc6-f89b-42da-b0e8-34c5391bb093</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-014] Verify print result via system dialog</t>
+  </si>
+  <si>
+    <t>6ec270f5-c255-4fcc-ba9d-b25361a6beff</t>
+  </si>
+  <si>
+    <t>[TC-ANAL-015] Verify result metadata (time, location, device)</t>
+  </si>
+  <si>
+    <t>2e867407-26b3-4042-a66e-dbb0628f6aa4</t>
   </si>
   <si>
     <t>Splash Screen</t>
@@ -1691,241 +1691,241 @@
     <t>Module: Splash Screen</t>
   </si>
   <si>
-    <t>[TC-SPLA-001] should validate Splash Screen criteria 1</t>
-  </si>
-  <si>
-    <t>a6f4c4ca-acb3-43ab-a3c3-0d76601d5ce9</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-002] should validate Splash Screen criteria 2</t>
-  </si>
-  <si>
-    <t>45ed9c36-66b1-4c5b-b2fd-7bf600848da4</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-003] should validate Splash Screen criteria 3</t>
-  </si>
-  <si>
-    <t>5aef046e-3843-4840-8aeb-842852f038b1</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-004] should validate Splash Screen criteria 4</t>
-  </si>
-  <si>
-    <t>71863047-724c-4cd2-84e0-0f09bb9fd9fa</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-005] should validate Splash Screen criteria 5</t>
-  </si>
-  <si>
-    <t>4b36c6e7-38bf-4496-874b-ea059b4f6856</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-006] should validate Splash Screen criteria 6</t>
-  </si>
-  <si>
-    <t>b3a98ece-9728-4b93-a33d-7020c282ebce</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-007] should validate Splash Screen criteria 7</t>
-  </si>
-  <si>
-    <t>f9a7566c-c1a2-4b38-9924-bfd376d2ed8c</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-008] should validate Splash Screen criteria 8</t>
-  </si>
-  <si>
-    <t>1d1be489-8141-4f62-8167-c00f2a64bac2</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-009] should validate Splash Screen criteria 9</t>
-  </si>
-  <si>
-    <t>6cc8a1e5-915b-46c2-95a4-ff58d1f98e3f</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-010] should validate Splash Screen criteria 10</t>
-  </si>
-  <si>
-    <t>f56a3a14-07ea-4a81-983b-1f28606ee1c8</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-011] should validate Splash Screen criteria 11</t>
-  </si>
-  <si>
-    <t>7ca42e85-d251-4456-85b2-243a87d3db17</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-012] should validate Splash Screen criteria 12</t>
-  </si>
-  <si>
-    <t>cd16d58b-5c53-4d1d-baf3-bf05078a44c1</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-013] should validate Splash Screen criteria 13</t>
-  </si>
-  <si>
-    <t>7d84de21-1f3b-4491-8298-e57dd838d6e5</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-014] should validate Splash Screen criteria 14</t>
-  </si>
-  <si>
-    <t>4fec2709-eb63-4db1-b8ba-e1db5ee6d4af</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-015] should validate Splash Screen criteria 15</t>
-  </si>
-  <si>
-    <t>c73576f5-8cc8-40e5-9b3f-c3640bd7a14f</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-016] should validate Splash Screen criteria 16</t>
-  </si>
-  <si>
-    <t>2cd62691-b8ef-4595-af1d-09ac3237912b</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-017] should validate Splash Screen criteria 17</t>
-  </si>
-  <si>
-    <t>75b1bfbd-1a46-4291-a844-57d734aab5df</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-018] should validate Splash Screen criteria 18</t>
-  </si>
-  <si>
-    <t>031cd717-5c3f-4ea7-9076-dfb67644f6da</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-019] should validate Splash Screen criteria 19</t>
-  </si>
-  <si>
-    <t>0a66f678-867b-4d11-89d2-8fa03bb1dade</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-020] should validate Splash Screen criteria 20</t>
-  </si>
-  <si>
-    <t>c9068739-a2bb-4a4c-8318-69e7baf94615</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-021] should validate Splash Screen criteria 21</t>
-  </si>
-  <si>
-    <t>543f1e40-90cf-48c4-a93d-0d7420b7ffe6</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-022] should validate Splash Screen criteria 22</t>
-  </si>
-  <si>
-    <t>82f587a7-b042-4fc2-80ed-f4dea05037ae</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-023] should validate Splash Screen criteria 23</t>
-  </si>
-  <si>
-    <t>45c319c4-baa4-48db-99f1-1b2b05498cea</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-024] should validate Splash Screen criteria 24</t>
-  </si>
-  <si>
-    <t>5794664c-2dc1-4a26-816d-4d2ef368f187</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-025] should validate Splash Screen criteria 25</t>
-  </si>
-  <si>
-    <t>ca3bdf08-f257-4df9-9459-29ca8c40161c</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-026] should validate Splash Screen criteria 26</t>
-  </si>
-  <si>
-    <t>9112e77b-9c94-4332-9307-41f95ee1ad96</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-027] should validate Splash Screen criteria 27</t>
-  </si>
-  <si>
-    <t>9412b3ed-1d81-4e09-ad3c-0c8e46ff5230</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-028] should validate Splash Screen criteria 28</t>
-  </si>
-  <si>
-    <t>7cba900b-cd4d-4ed4-a27e-ba7f2a0a20c2</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-029] should validate Splash Screen criteria 29</t>
-  </si>
-  <si>
-    <t>f9262f15-9b8f-4507-b99e-d6d3ddf5fab1</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-030] should validate Splash Screen criteria 30</t>
-  </si>
-  <si>
-    <t>02d3d49c-7350-426a-bbb5-b0625156614d</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-031] should validate Splash Screen criteria 31</t>
-  </si>
-  <si>
-    <t>577a8ec1-bf24-4679-9b64-aa4d0aa1e461</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-032] should validate Splash Screen criteria 32</t>
-  </si>
-  <si>
-    <t>f17611cf-97f4-4dbe-8996-a58fe7260c2c</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-033] should validate Splash Screen criteria 33</t>
-  </si>
-  <si>
-    <t>2b938a38-12fd-419e-9b70-50284744cfb7</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-034] should validate Splash Screen criteria 34</t>
-  </si>
-  <si>
-    <t>95f08484-f878-48d7-b99f-3437ffbcf05a</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-035] should validate Splash Screen criteria 35</t>
-  </si>
-  <si>
-    <t>3a57909f-f471-4fc9-87eb-df7d20c002c3</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-036] should validate Splash Screen criteria 36</t>
-  </si>
-  <si>
-    <t>c7c451d5-5e9d-4d88-ab9f-905f67266916</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-037] should validate Splash Screen criteria 37</t>
-  </si>
-  <si>
-    <t>d45e5384-3fc9-4f82-9e83-11e43fbc1c78</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-038] should validate Splash Screen criteria 38</t>
-  </si>
-  <si>
-    <t>727b26d7-f0fa-47d7-8e88-d0b3ba8ee3b2</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-039] should validate Splash Screen criteria 39</t>
-  </si>
-  <si>
-    <t>63921b20-9402-402b-a4a2-b076c1e4f9aa</t>
-  </si>
-  <si>
-    <t>[TC-SPLA-040] should validate Splash Screen criteria 40</t>
+    <t>[TC-SPLA-001] Verify splash screen displays app logo</t>
+  </si>
+  <si>
+    <t>106c91b7-8f75-4fae-ad24-bfa7e53a0738</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-002] Verify splash screen animates correctly</t>
+  </si>
+  <si>
+    <t>768ac075-f7ce-4071-9ed2-5b6cec5a4600</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-003] Verify splash screen hides status bar</t>
+  </si>
+  <si>
+    <t>88f39908-84cb-49e6-b07e-96474596cc98</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-004] Verify background color matches theme</t>
+  </si>
+  <si>
+    <t>6248ac70-885a-484d-9657-2ccb2cc2b0b3</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-005] Verify splash screen lasts minimum 1 second</t>
+  </si>
+  <si>
+    <t>021224e6-9996-4d73-b847-60c2cf80a637</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-006] Verify app routing checks authentication state</t>
+  </si>
+  <si>
+    <t>f50bbb31-15ff-419c-b4f4-6ef82d49ce8a</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-007] Verify auto-login routes to Dashboard</t>
+  </si>
+  <si>
+    <t>4bb56753-6c37-418c-bd20-c48a5cad8d95</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-008] Verify unauthenticated routes to Login</t>
+  </si>
+  <si>
+    <t>689a74e8-887b-4d4e-9c13-ef521a6f7644</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-009] Verify first-time launch routes to Onboarding</t>
+  </si>
+  <si>
+    <t>f9d270b3-9c28-4552-b488-4703b659781d</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-010] Verify deep link routing intercepts splash</t>
+  </si>
+  <si>
+    <t>e91ed41f-a00b-4712-abec-6dfe9e5458f4</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-011] Verify forced app update check during splash</t>
+  </si>
+  <si>
+    <t>8ba29bba-6b46-4149-a186-4759ff85f60b</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-012] Verify maintenance mode check during splash</t>
+  </si>
+  <si>
+    <t>d84efd5e-57d3-4515-8923-8802a96f419b</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-013] Verify network availability check</t>
+  </si>
+  <si>
+    <t>9aa2cd56-adb5-4d28-8986-72e6e17c8793</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-014] Verify local database migration runs</t>
+  </si>
+  <si>
+    <t>bb2de51e-8e36-4b9d-a7b9-99664297631b</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-015] Verify splash screen on cold start</t>
+  </si>
+  <si>
+    <t>7aa3481a-0945-4fdc-b5c2-e292ffccb3d5</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-016] Verify splash screen on warm start</t>
+  </si>
+  <si>
+    <t>ed47a7a7-9a07-4a89-a3ec-461f5fa4e98a</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-017] Verify error boundary catches startup crashes</t>
+  </si>
+  <si>
+    <t>2570eee0-ad10-423c-9eb7-f1e431cc0725</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-018] Verify analytics SDK initializes</t>
+  </si>
+  <si>
+    <t>05cdba8e-5b11-45f5-86a0-15047cae11ca</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-019] Verify crash reporting SDK initializes</t>
+  </si>
+  <si>
+    <t>68917395-6d87-44a2-a7b1-62db60dab3da</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-020] Verify push notification token refresh</t>
+  </si>
+  <si>
+    <t>08b23bec-8d1b-47bd-91be-0319df7f1430</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-021] Verify localization strings load</t>
+  </si>
+  <si>
+    <t>14471686-2dbe-408e-9f5e-c03bec465f23</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-022] Verify custom fonts load before routing</t>
+  </si>
+  <si>
+    <t>0cb66051-9de5-4e15-9c46-6f64dfd0137e</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-023] Verify theme preference loads before routing</t>
+  </si>
+  <si>
+    <t>99d03ba6-43a8-47f8-8a54-f3026f4e7922</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-024] Verify splash screen is accessible (aria-hidden)</t>
+  </si>
+  <si>
+    <t>77e2c388-2352-42ba-abe0-b3d6ad770f34</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-025] Verify splash screen memory footprint</t>
+  </si>
+  <si>
+    <t>f6e14077-e169-46fc-ace8-a8e53834fc76</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-026] Verify splash screen on slow network</t>
+  </si>
+  <si>
+    <t>25d686d9-3323-446b-8be3-c4ec6caedf62</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-027] Verify splash timeout fallback</t>
+  </si>
+  <si>
+    <t>14cd7224-1a90-413d-8774-b803bafeb5d1</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-028] Verify offline mode routing</t>
+  </si>
+  <si>
+    <t>864bbd0a-e699-4bb3-b3f0-19dc7683432e</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-029] Verify caching of static assets</t>
+  </si>
+  <si>
+    <t>c5bc51a2-0f59-4c07-aea0-fc37d71b82ac</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-030] Verify root component mounts successfully</t>
+  </si>
+  <si>
+    <t>f3e2d071-a096-4a59-a307-b772ad38d48e</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-031] Verify redux store hydration</t>
+  </si>
+  <si>
+    <t>d3abde0f-da6f-4bd1-ad3b-74e86a0e42e4</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-032] Verify global interceptors setup</t>
+  </si>
+  <si>
+    <t>bc128371-cf1f-4b5e-8a87-aa4681aa479d</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-033] Verify WebSocket connection initiated</t>
+  </si>
+  <si>
+    <t>0f8a87ac-ecd0-4f86-bd6d-c1ef6f1cd30e</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-034] Verify biometric prompt triggers if enabled</t>
+  </si>
+  <si>
+    <t>d8a48af5-a7a0-4ba4-9122-a5919c06aeee</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-035] Verify permission requests deferred until needed</t>
+  </si>
+  <si>
+    <t>031c9536-3b1b-45c6-9373-7cd4d1ff4dd8</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-036] Verify splash screen resolution on 4K displays</t>
+  </si>
+  <si>
+    <t>871f6c03-0897-4579-8558-05f54607a224</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-037] Verify splash screen on notch devices</t>
+  </si>
+  <si>
+    <t>0f640988-c0f3-41e4-b574-c3919a07f5c9</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-038] Verify system dark mode override</t>
+  </si>
+  <si>
+    <t>43f22709-3bf8-45e5-871c-40ff4d003b8b</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-039] Verify system font scaling affects logo</t>
+  </si>
+  <si>
+    <t>50a4585a-a3df-40ff-bedb-55ce7eeeb180</t>
+  </si>
+  <si>
+    <t>[TC-SPLA-040] Verify landscape orientation handles splash correctly</t>
   </si>
   <si>
     <t>Metric</t>
@@ -2403,7 +2403,7 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -2449,7 +2449,7 @@
         <v>11</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -2541,7 +2541,7 @@
         <v>11</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -2794,7 +2794,7 @@
         <v>11</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -3185,7 +3185,7 @@
         <v>11</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="s">
         <v>12</v>
@@ -3300,7 +3300,7 @@
         <v>11</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="s">
         <v>12</v>
@@ -3898,7 +3898,7 @@
         <v>11</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="s">
         <v>12</v>
@@ -3944,7 +3944,7 @@
         <v>11</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="s">
         <v>12</v>
@@ -4197,7 +4197,7 @@
         <v>11</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="s">
         <v>12</v>
@@ -4496,7 +4496,7 @@
         <v>11</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="s">
         <v>12</v>
@@ -5393,7 +5393,7 @@
         <v>11</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133" t="s">
         <v>12</v>
@@ -5508,7 +5508,7 @@
         <v>11</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" t="s">
         <v>12</v>
@@ -5692,7 +5692,7 @@
         <v>11</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="s">
         <v>12</v>
@@ -6152,7 +6152,7 @@
         <v>11</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G166" t="s">
         <v>12</v>
@@ -6290,7 +6290,7 @@
         <v>11</v>
       </c>
       <c r="F172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" t="s">
         <v>12</v>
@@ -6336,7 +6336,7 @@
         <v>11</v>
       </c>
       <c r="F174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G174" t="s">
         <v>12</v>
@@ -6405,7 +6405,7 @@
         <v>11</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" t="s">
         <v>12</v>
@@ -6911,7 +6911,7 @@
         <v>11</v>
       </c>
       <c r="F199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" t="s">
         <v>12</v>
@@ -7371,7 +7371,7 @@
         <v>11</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G219" t="s">
         <v>12</v>
@@ -7509,7 +7509,7 @@
         <v>11</v>
       </c>
       <c r="F225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G225" t="s">
         <v>12</v>
@@ -7716,7 +7716,7 @@
         <v>11</v>
       </c>
       <c r="F234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G234" t="s">
         <v>12</v>
@@ -8015,7 +8015,7 @@
         <v>11</v>
       </c>
       <c r="F247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G247" t="s">
         <v>12</v>
@@ -8797,7 +8797,7 @@
         <v>11</v>
       </c>
       <c r="F281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G281" t="s">
         <v>12</v>
@@ -9345,7 +9345,7 @@
         <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -9391,7 +9391,7 @@
         <v>11</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -9483,7 +9483,7 @@
         <v>11</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -9736,7 +9736,7 @@
         <v>11</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -10127,7 +10127,7 @@
         <v>11</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="s">
         <v>12</v>
@@ -10242,7 +10242,7 @@
         <v>11</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="s">
         <v>12</v>
@@ -10840,7 +10840,7 @@
         <v>11</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="s">
         <v>12</v>
@@ -10886,7 +10886,7 @@
         <v>11</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="s">
         <v>12</v>
@@ -11139,7 +11139,7 @@
         <v>11</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="s">
         <v>12</v>
@@ -11438,7 +11438,7 @@
         <v>11</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="s">
         <v>12</v>
@@ -12335,7 +12335,7 @@
         <v>11</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133" t="s">
         <v>12</v>
@@ -12450,7 +12450,7 @@
         <v>11</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" t="s">
         <v>12</v>
@@ -12634,7 +12634,7 @@
         <v>11</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="s">
         <v>12</v>
@@ -13094,7 +13094,7 @@
         <v>11</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G166" t="s">
         <v>12</v>
@@ -13232,7 +13232,7 @@
         <v>11</v>
       </c>
       <c r="F172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" t="s">
         <v>12</v>
@@ -13278,7 +13278,7 @@
         <v>11</v>
       </c>
       <c r="F174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G174" t="s">
         <v>12</v>
@@ -13347,7 +13347,7 @@
         <v>11</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" t="s">
         <v>12</v>
@@ -13853,7 +13853,7 @@
         <v>11</v>
       </c>
       <c r="F199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" t="s">
         <v>12</v>
@@ -14313,7 +14313,7 @@
         <v>11</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G219" t="s">
         <v>12</v>
@@ -14451,7 +14451,7 @@
         <v>11</v>
       </c>
       <c r="F225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G225" t="s">
         <v>12</v>
@@ -14658,7 +14658,7 @@
         <v>11</v>
       </c>
       <c r="F234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G234" t="s">
         <v>12</v>
@@ -14957,7 +14957,7 @@
         <v>11</v>
       </c>
       <c r="F247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G247" t="s">
         <v>12</v>
@@ -15739,7 +15739,7 @@
         <v>11</v>
       </c>
       <c r="F281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G281" t="s">
         <v>12</v>
@@ -16357,7 +16357,7 @@
         <v>645</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
